--- a/3_Code/output/jarak_kurir_harian_dan_total_paket.xlsx
+++ b/3_Code/output/jarak_kurir_harian_dan_total_paket.xlsx
@@ -1,34 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="21001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21001"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPB\TESIS\PENELITIAN\CODE\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA25069E-DBE6-44E6-8A02-3D07AE3FBE1F}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E4CEE3-3046-4951-AA4F-A915F822AEEB}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Pivot NIK" sheetId="2" r:id="rId1"/>
-    <sheet name="Pivot Tanggal" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="7" r:id="rId1"/>
+    <sheet name="Pivot Tanggal Paket" sheetId="6" r:id="rId2"/>
     <sheet name="jarak_kurir_harian" sheetId="1" r:id="rId3"/>
+    <sheet name="Pivot NIK" sheetId="2" r:id="rId4"/>
+    <sheet name="Pivot Tanggal Jarak" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">jarak_kurir_harian!$A$1:$D$648</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="5" r:id="rId6"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="42">
   <si>
     <t>205_id</t>
   </si>
@@ -131,12 +133,36 @@
   <si>
     <t>Count of 205_id</t>
   </si>
+  <si>
+    <t>Average of total_distance_km</t>
+  </si>
+  <si>
+    <t>AVG Jarak</t>
+  </si>
+  <si>
+    <t>MAD</t>
+  </si>
+  <si>
+    <t>Kurir</t>
+  </si>
+  <si>
+    <t>Deviasi</t>
+  </si>
+  <si>
+    <t>STD</t>
+  </si>
+  <si>
+    <t>MAD Jarak Tempuh</t>
+  </si>
+  <si>
+    <t>AVG Paket</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,16 +178,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -169,11 +215,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -183,11 +247,150 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4181,7 +4384,483 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{17E076F9-C55C-451E-8131-7DFF3FC26389}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{21FB3EBC-14C7-4FAB-BF5B-B660E0644095}" name="PivotTable5" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="42">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="24">
+        <item h="1" x="21"/>
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item h="1" x="4"/>
+        <item h="1" x="5"/>
+        <item h="1" x="6"/>
+        <item h="1" x="22"/>
+        <item h="1" x="18"/>
+        <item h="1" x="7"/>
+        <item h="1" x="8"/>
+        <item h="1" x="9"/>
+        <item h="1" x="10"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="20"/>
+        <item h="1" x="17"/>
+        <item h="1" x="19"/>
+        <item h="1" x="13"/>
+        <item h="1" x="14"/>
+        <item h="1" x="15"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="40">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of total_awb_harian" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87B6BFC0-8CFB-499E-ABAC-3ADB01F8CD8D}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A2:D26" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField dataField="1" showAll="0">
+      <items count="42">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="24">
+        <item x="21"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="22"/>
+        <item x="18"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="20"/>
+        <item x="17"/>
+        <item x="19"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="24">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Count of 205_id" fld="0" subtotal="count" baseField="1" baseItem="0"/>
+    <dataField name="Sum of total_awb_harian" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Average of total_distance_km" fld="3" subtotal="average" baseField="1" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="0">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="2">
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="2">
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="2">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="2">
+            <x v="12"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="2">
+            <x v="12"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="4">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1">
+            <x v="22"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1">
+            <x v="22"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{17E076F9-C55C-451E-8131-7DFF3FC26389}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:D45" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -4405,11 +5084,56 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2DCCD583-973C-4D70-8B25-90B4064EA343}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:C27" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BECCD010-E5DB-46BD-A004-8CD073C51B46}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A2:D26" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="42">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" showAll="0">
       <items count="24">
         <item x="21"/>
@@ -4439,7 +5163,7 @@
       </items>
     </pivotField>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="1"/>
@@ -4521,18 +5245,82 @@
   <colFields count="1">
     <field x="-2"/>
   </colFields>
-  <colItems count="2">
+  <colItems count="3">
     <i>
       <x/>
     </i>
     <i i="1">
       <x v="1"/>
     </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
   </colItems>
-  <dataFields count="2">
-    <dataField name="Count of 205_id" fld="0" subtotal="count" baseField="1" baseItem="0"/>
+  <dataFields count="3">
+    <dataField name="Kurir" fld="0" subtotal="count" baseField="1" baseItem="3"/>
     <dataField name="Sum of total_awb_harian" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Average of total_distance_km" fld="3" subtotal="average" baseField="0" baseItem="1953018073"/>
   </dataFields>
+  <formats count="6">
+    <format dxfId="17">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="2">
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="16">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="2">
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="15">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="2">
+            <x v="12"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="2">
+            <x v="12"/>
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1">
+            <x v="22"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="1">
+            <x v="22"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -4865,624 +5653,348 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEEDBC97-83BF-473C-9ED6-9E9D09C223F1}">
-  <dimension ref="A3:G45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E71B49D2-00A1-4512-8C2E-65DC93EF1797}">
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>10074145</v>
+        <v>10001245</v>
       </c>
       <c r="B4" s="4">
-        <v>19</v>
-      </c>
-      <c r="C4" s="4">
-        <v>824</v>
-      </c>
-      <c r="D4" s="4">
-        <v>1138.5311440688481</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4">
-        <f>AVERAGE(D4:D44)</f>
-        <v>463.02053115896717</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
+        <v>10003936</v>
+      </c>
+      <c r="B5" s="4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>10006503</v>
+      </c>
+      <c r="B6" s="4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>10009662</v>
+      </c>
+      <c r="B7" s="4">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>10011641</v>
+      </c>
+      <c r="B8" s="4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>10014010</v>
+      </c>
+      <c r="B9" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>10014255</v>
+      </c>
+      <c r="B10" s="4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>10014704</v>
+      </c>
+      <c r="B11" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>10024737</v>
+      </c>
+      <c r="B12" s="4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>10024880</v>
+      </c>
+      <c r="B13" s="4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>10025537</v>
+      </c>
+      <c r="B14" s="4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>10025538</v>
+      </c>
+      <c r="B15" s="4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>10029570</v>
+      </c>
+      <c r="B16" s="4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>10031843</v>
+      </c>
+      <c r="B17" s="4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>10031844</v>
+      </c>
+      <c r="B18" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>10031845</v>
+      </c>
+      <c r="B19" s="4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>10035125</v>
+      </c>
+      <c r="B20" s="4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>10038027</v>
+      </c>
+      <c r="B21" s="4">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>10046352</v>
+      </c>
+      <c r="B22" s="4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>10046795</v>
+      </c>
+      <c r="B23" s="4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>10047909</v>
+      </c>
+      <c r="B24" s="4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>10052254</v>
+      </c>
+      <c r="B25" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
         <v>10053112</v>
       </c>
-      <c r="B5" s="4">
-        <v>16</v>
-      </c>
-      <c r="C5" s="4">
-        <v>944</v>
-      </c>
-      <c r="D5" s="4">
-        <v>830.89388482273898</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>10035125</v>
-      </c>
-      <c r="B6" s="4">
-        <v>17</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1078</v>
-      </c>
-      <c r="D6" s="4">
-        <v>685.17578694000531</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>10080492</v>
-      </c>
-      <c r="B7" s="4">
-        <v>16</v>
-      </c>
-      <c r="C7" s="4">
-        <v>644</v>
-      </c>
-      <c r="D7" s="4">
-        <v>677.42722417322159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>10014010</v>
-      </c>
-      <c r="B8" s="4">
-        <v>17</v>
-      </c>
-      <c r="C8" s="4">
-        <v>965</v>
-      </c>
-      <c r="D8" s="4">
-        <v>674.74857312562904</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="B26" s="4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
         <v>10055658</v>
       </c>
-      <c r="B9" s="4">
-        <v>17</v>
-      </c>
-      <c r="C9" s="4">
-        <v>1087</v>
-      </c>
-      <c r="D9" s="4">
-        <v>579.88402414992947</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>10047909</v>
-      </c>
-      <c r="B10" s="4">
-        <v>16</v>
-      </c>
-      <c r="C10" s="4">
-        <v>874</v>
-      </c>
-      <c r="D10" s="4">
-        <v>577.06195207205838</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>10003936</v>
-      </c>
-      <c r="B11" s="4">
-        <v>17</v>
-      </c>
-      <c r="C11" s="4">
-        <v>1058</v>
-      </c>
-      <c r="D11" s="4">
-        <v>548.77185908791364</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>10025537</v>
-      </c>
-      <c r="B12" s="4">
-        <v>17</v>
-      </c>
-      <c r="C12" s="4">
-        <v>964</v>
-      </c>
-      <c r="D12" s="4">
-        <v>533.39929235040756</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+      <c r="B27" s="4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
         <v>10062125</v>
       </c>
-      <c r="B13" s="4">
-        <v>18</v>
-      </c>
-      <c r="C13" s="4">
-        <v>1215</v>
-      </c>
-      <c r="D13" s="4">
-        <v>532.44432505522786</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+      <c r="B28" s="4">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>10064690</v>
+      </c>
+      <c r="B29" s="4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
         <v>10068449</v>
       </c>
-      <c r="B14" s="4">
-        <v>17</v>
-      </c>
-      <c r="C14" s="4">
-        <v>1097</v>
-      </c>
-      <c r="D14" s="4">
-        <v>527.98415406592778</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>10031845</v>
-      </c>
-      <c r="B15" s="4">
-        <v>15</v>
-      </c>
-      <c r="C15" s="4">
-        <v>818</v>
-      </c>
-      <c r="D15" s="4">
-        <v>517.27020254185572</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>10038027</v>
-      </c>
-      <c r="B16" s="4">
-        <v>16</v>
-      </c>
-      <c r="C16" s="4">
-        <v>1075</v>
-      </c>
-      <c r="D16" s="4">
-        <v>513.38591052848267</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>10024737</v>
-      </c>
-      <c r="B17" s="4">
-        <v>17</v>
-      </c>
-      <c r="C17" s="4">
-        <v>973</v>
-      </c>
-      <c r="D17" s="4">
-        <v>507.78080929216867</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>10024880</v>
-      </c>
-      <c r="B18" s="4">
-        <v>16</v>
-      </c>
-      <c r="C18" s="4">
-        <v>1054</v>
-      </c>
-      <c r="D18" s="4">
-        <v>503.5859470233342</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>10079995</v>
-      </c>
-      <c r="B19" s="4">
-        <v>17</v>
-      </c>
-      <c r="C19" s="4">
-        <v>785</v>
-      </c>
-      <c r="D19" s="4">
-        <v>502.18220534542974</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>10046795</v>
-      </c>
-      <c r="B20" s="4">
-        <v>17</v>
-      </c>
-      <c r="C20" s="4">
-        <v>991</v>
-      </c>
-      <c r="D20" s="4">
-        <v>477.57049284952905</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>10064690</v>
-      </c>
-      <c r="B21" s="4">
-        <v>18</v>
-      </c>
-      <c r="C21" s="4">
-        <v>737</v>
-      </c>
-      <c r="D21" s="4">
-        <v>476.64115217340657</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>10014704</v>
-      </c>
-      <c r="B22" s="4">
-        <v>16</v>
-      </c>
-      <c r="C22" s="4">
-        <v>929</v>
-      </c>
-      <c r="D22" s="4">
-        <v>471.12254618230116</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>10001245</v>
-      </c>
-      <c r="B23" s="4">
-        <v>17</v>
-      </c>
-      <c r="C23" s="4">
-        <v>863</v>
-      </c>
-      <c r="D23" s="4">
-        <v>467.60127816058917</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>10011641</v>
-      </c>
-      <c r="B24" s="4">
-        <v>18</v>
-      </c>
-      <c r="C24" s="4">
-        <v>977</v>
-      </c>
-      <c r="D24" s="4">
-        <v>463.85368450106949</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>10031844</v>
-      </c>
-      <c r="B25" s="4">
-        <v>17</v>
-      </c>
-      <c r="C25" s="4">
-        <v>715</v>
-      </c>
-      <c r="D25" s="4">
-        <v>461.80807612739619</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
-        <v>10006503</v>
-      </c>
-      <c r="B26" s="4">
-        <v>17</v>
-      </c>
-      <c r="C26" s="4">
-        <v>975</v>
-      </c>
-      <c r="D26" s="4">
-        <v>453.92259755301927</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>10014255</v>
-      </c>
-      <c r="B27" s="4">
-        <v>16</v>
-      </c>
-      <c r="C27" s="4">
-        <v>1013</v>
-      </c>
-      <c r="D27" s="4">
-        <v>451.08950831208591</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <v>10078132</v>
-      </c>
-      <c r="B28" s="4">
-        <v>18</v>
-      </c>
-      <c r="C28" s="4">
-        <v>957</v>
-      </c>
-      <c r="D28" s="4">
-        <v>425.20801889729626</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <v>10072947</v>
-      </c>
-      <c r="B29" s="4">
-        <v>16</v>
-      </c>
-      <c r="C29" s="4">
-        <v>805</v>
-      </c>
-      <c r="D29" s="4">
-        <v>418.90482802917762</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
-        <v>10029570</v>
-      </c>
       <c r="B30" s="4">
-        <v>16</v>
-      </c>
-      <c r="C30" s="4">
-        <v>1007</v>
-      </c>
-      <c r="D30" s="4">
-        <v>418.30785318939013</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>10072594</v>
       </c>
       <c r="B31" s="4">
-        <v>17</v>
-      </c>
-      <c r="C31" s="4">
-        <v>789</v>
-      </c>
-      <c r="D31" s="4">
-        <v>417.14019327926013</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
+        <v>10072947</v>
+      </c>
+      <c r="B32" s="4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>10073494</v>
+      </c>
+      <c r="B33" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>10073889</v>
+      </c>
+      <c r="B34" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>10074145</v>
+      </c>
+      <c r="B35" s="4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>10076349</v>
+      </c>
+      <c r="B36" s="4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>10078132</v>
+      </c>
+      <c r="B37" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>10079995</v>
+      </c>
+      <c r="B38" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
         <v>10080481</v>
       </c>
-      <c r="B32" s="4">
-        <v>17</v>
-      </c>
-      <c r="C32" s="4">
-        <v>603</v>
-      </c>
-      <c r="D32" s="4">
-        <v>415.03376896121887</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
-        <v>10025538</v>
-      </c>
-      <c r="B33" s="4">
-        <v>16</v>
-      </c>
-      <c r="C33" s="4">
-        <v>803</v>
-      </c>
-      <c r="D33" s="4">
-        <v>404.60756680505193</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
-        <v>10031843</v>
-      </c>
-      <c r="B34" s="4">
-        <v>17</v>
-      </c>
-      <c r="C34" s="4">
-        <v>802</v>
-      </c>
-      <c r="D34" s="4">
-        <v>403.27583716541915</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
-        <v>10052254</v>
-      </c>
-      <c r="B35" s="4">
-        <v>15</v>
-      </c>
-      <c r="C35" s="4">
-        <v>766</v>
-      </c>
-      <c r="D35" s="4">
-        <v>387.27744420315918</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
-        <v>10073889</v>
-      </c>
-      <c r="B36" s="4">
-        <v>15</v>
-      </c>
-      <c r="C36" s="4">
-        <v>708</v>
-      </c>
-      <c r="D36" s="4">
-        <v>380.55131070778793</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
-        <v>10076349</v>
-      </c>
-      <c r="B37" s="4">
-        <v>18</v>
-      </c>
-      <c r="C37" s="4">
-        <v>800</v>
-      </c>
-      <c r="D37" s="4">
-        <v>366.46647639493449</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
-        <v>10009662</v>
-      </c>
-      <c r="B38" s="4">
-        <v>17</v>
-      </c>
-      <c r="C38" s="4">
-        <v>982</v>
-      </c>
-      <c r="D38" s="4">
-        <v>363.52175631590325</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
+      <c r="B39" s="4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>10080492</v>
+      </c>
+      <c r="B40" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
         <v>10080596</v>
       </c>
-      <c r="B39" s="4">
-        <v>12</v>
-      </c>
-      <c r="C39" s="4">
-        <v>414</v>
-      </c>
-      <c r="D39" s="4">
-        <v>283.24603271438605</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
-        <v>10073494</v>
-      </c>
-      <c r="B40" s="4">
-        <v>13</v>
-      </c>
-      <c r="C40" s="4">
-        <v>588</v>
-      </c>
-      <c r="D40" s="4">
-        <v>239.05656298426646</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
-        <v>10046352</v>
-      </c>
       <c r="B41" s="4">
-        <v>15</v>
-      </c>
-      <c r="C41" s="4">
-        <v>542</v>
-      </c>
-      <c r="D41" s="4">
-        <v>225.80996102190471</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>10080747</v>
       </c>
       <c r="B42" s="4">
-        <v>7</v>
-      </c>
-      <c r="C42" s="4">
-        <v>252</v>
-      </c>
-      <c r="D42" s="4">
-        <v>127.36792410229592</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <v>10080624</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="B43" s="4">
-        <v>7</v>
-      </c>
-      <c r="C43" s="4">
-        <v>160</v>
-      </c>
-      <c r="D43" s="4">
-        <v>78.465934254304287</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
-        <v>10080526</v>
-      </c>
-      <c r="B44" s="4">
-        <v>7</v>
-      </c>
-      <c r="C44" s="4">
-        <v>96</v>
-      </c>
-      <c r="D44" s="4">
-        <v>55.463677989325248</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B45" s="4">
-        <v>647</v>
-      </c>
-      <c r="C45" s="4">
-        <v>33729</v>
-      </c>
-      <c r="D45" s="4">
-        <v>18983.841777517657</v>
+        <v>3286</v>
       </c>
     </row>
   </sheetData>
@@ -5491,205 +6003,285 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3F94BF-6DF3-4E0E-BB3C-5F89986CEC75}">
-  <dimension ref="A3:C27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3C87F9-F0B4-48DF-B526-64D8EFC8A869}">
+  <dimension ref="A2:S73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B2" t="s">
         <v>33</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="12">
+        <f>(B70+F70+J73+N72+R72)/5</f>
+        <v>16.865398165637252</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2.8650753483456879</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B4" s="4">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C4" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="D4" s="4">
+        <v>3.9593215387067451</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="4">
+        <v>35</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1243</v>
+      </c>
+      <c r="D5" s="4">
+        <v>23.859197406172427</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4">
         <v>33</v>
       </c>
-      <c r="C5" s="4">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4">
-        <v>35</v>
-      </c>
       <c r="C6" s="4">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4">
-        <v>33</v>
-      </c>
-      <c r="C7" s="4">
         <v>2649</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="D6" s="4">
+        <v>46.414215339600659</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B7" s="8">
         <v>37</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C7" s="8">
         <v>3773</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="8">
+        <v>50.419868716772477</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="8">
+        <v>37</v>
+      </c>
+      <c r="C8" s="8">
+        <v>3005</v>
+      </c>
+      <c r="D8" s="8">
+        <v>44.762473658203021</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="4">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C9" s="4">
-        <v>3005</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2272</v>
+      </c>
+      <c r="D9" s="4">
+        <v>33.085821379379027</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="4">
+        <v>40</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1012</v>
+      </c>
+      <c r="D10" s="4">
+        <v>15.885232193425619</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2.6539806782346749</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="4">
+        <v>3</v>
+      </c>
+      <c r="C12" s="4">
+        <v>3</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1.6229573812050735</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4">
+        <v>40</v>
+      </c>
+      <c r="C13" s="4">
+        <v>279</v>
+      </c>
+      <c r="D13" s="4">
+        <v>6.8353126501307218</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4">
+        <v>38</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1821</v>
+      </c>
+      <c r="D14" s="4">
+        <v>29.39627924808423</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="8">
+        <v>40</v>
+      </c>
+      <c r="C15" s="8">
+        <v>3140</v>
+      </c>
+      <c r="D15" s="8">
+        <v>38.506714860538501</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8">
         <v>39</v>
       </c>
-      <c r="C10" s="4">
-        <v>2272</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4">
-        <v>40</v>
-      </c>
-      <c r="C11" s="4">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="4">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="4">
-        <v>3</v>
-      </c>
-      <c r="C13" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="4">
-        <v>40</v>
-      </c>
-      <c r="C14" s="4">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="4">
-        <v>38</v>
-      </c>
-      <c r="C15" s="4">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="4">
-        <v>40</v>
-      </c>
-      <c r="C16" s="4">
-        <v>3140</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="8">
+        <v>3889</v>
+      </c>
+      <c r="D16" s="8">
+        <v>54.384789219770795</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="4">
         <v>39</v>
       </c>
       <c r="C17" s="4">
-        <v>3889</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1394</v>
+      </c>
+      <c r="D17" s="4">
+        <v>21.800645018658727</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="4">
         <v>39</v>
       </c>
       <c r="C18" s="4">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+      <c r="D18" s="4">
+        <v>6.3458594779350532</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B19" s="4">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="C19" s="4">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4">
+        <v>3.4545051302870071</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
@@ -5697,82 +6289,2267 @@
       <c r="C20" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" s="4">
+        <v>0.43429804578488568</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2.7939449756182539</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B22" s="4">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C22" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="D22" s="4">
+        <v>4.3579814490127369</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23" s="4">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C23" s="4">
+        <v>2749</v>
+      </c>
+      <c r="D23" s="4">
+        <v>36.95963924079836</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="4">
+        <v>37</v>
+      </c>
+      <c r="C24" s="4">
+        <v>2718</v>
+      </c>
+      <c r="D24" s="4">
+        <v>42.16288013995419</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="8">
+        <v>39</v>
+      </c>
+      <c r="C25" s="8">
+        <v>3286</v>
+      </c>
+      <c r="D25" s="8">
+        <v>44.140626027837882</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="4">
+        <v>647</v>
+      </c>
+      <c r="C26" s="4">
+        <v>33729</v>
+      </c>
+      <c r="D26" s="4">
+        <v>29.341331959069016</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A29" s="9">
+        <v>46231</v>
+      </c>
+      <c r="E29" s="9">
+        <v>46232</v>
+      </c>
+      <c r="I29" s="9">
+        <v>46240</v>
+      </c>
+      <c r="M29" s="9">
+        <v>46241</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="R30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="S30" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>10001245</v>
+      </c>
+      <c r="B31" s="4">
+        <v>100</v>
+      </c>
+      <c r="C31">
+        <f>ABS(B31-$B$68)</f>
+        <v>1.9729729729729684</v>
+      </c>
+      <c r="E31" s="3">
+        <v>10001245</v>
+      </c>
+      <c r="F31" s="4">
+        <v>80</v>
+      </c>
+      <c r="G31">
+        <f>ABS(F31-$F$68)</f>
+        <v>1.2162162162162105</v>
+      </c>
+      <c r="I31" s="3">
+        <v>10001245</v>
+      </c>
+      <c r="J31" s="4">
+        <v>71</v>
+      </c>
+      <c r="K31">
+        <f>ABS(J31-$J$71)</f>
+        <v>7.5</v>
+      </c>
+      <c r="M31" s="3">
+        <v>10001245</v>
+      </c>
+      <c r="N31" s="4">
+        <v>88</v>
+      </c>
+      <c r="O31">
+        <f>ABS(N31-$N$70)</f>
+        <v>11.717948717948715</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>10001245</v>
+      </c>
+      <c r="R31" s="4">
+        <v>84</v>
+      </c>
+      <c r="S31">
+        <f>ABS(R31-$R$70)</f>
+        <v>0.2564102564102626</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>10003936</v>
+      </c>
+      <c r="B32" s="4">
+        <v>119</v>
+      </c>
+      <c r="C32">
+        <f t="shared" ref="C32:C70" si="0">ABS(B32-$B$68)</f>
+        <v>17.027027027027032</v>
+      </c>
+      <c r="E32" s="3">
+        <v>10003936</v>
+      </c>
+      <c r="F32" s="4">
+        <v>86</v>
+      </c>
+      <c r="G32">
+        <f t="shared" ref="G32:G70" si="1">ABS(F32-$F$68)</f>
+        <v>4.7837837837837895</v>
+      </c>
+      <c r="I32" s="3">
+        <v>10003936</v>
+      </c>
+      <c r="J32" s="4">
+        <v>100</v>
+      </c>
+      <c r="K32">
+        <f t="shared" ref="K32:K73" si="2">ABS(J32-$J$71)</f>
+        <v>21.5</v>
+      </c>
+      <c r="M32" s="3">
+        <v>10003936</v>
+      </c>
+      <c r="N32" s="4">
+        <v>122</v>
+      </c>
+      <c r="O32">
+        <f t="shared" ref="O32:O72" si="3">ABS(N32-$N$70)</f>
+        <v>22.282051282051285</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>10003936</v>
+      </c>
+      <c r="R32" s="4">
+        <v>101</v>
+      </c>
+      <c r="S32">
+        <f t="shared" ref="S32:S72" si="4">ABS(R32-$R$70)</f>
+        <v>16.743589743589737</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>10006503</v>
+      </c>
+      <c r="B33" s="4">
+        <v>82</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="0"/>
+        <v>19.972972972972968</v>
+      </c>
+      <c r="E33" s="3">
+        <v>10006503</v>
+      </c>
+      <c r="F33" s="4">
+        <v>102</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="1"/>
+        <v>20.78378378378379</v>
+      </c>
+      <c r="I33" s="3">
+        <v>10006503</v>
+      </c>
+      <c r="J33" s="4">
+        <v>95</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="2"/>
+        <v>16.5</v>
+      </c>
+      <c r="M33" s="3">
+        <v>10006503</v>
+      </c>
+      <c r="N33" s="4">
+        <v>111</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="3"/>
+        <v>11.282051282051285</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>10006503</v>
+      </c>
+      <c r="R33" s="4">
+        <v>83</v>
+      </c>
+      <c r="S33">
+        <f t="shared" si="4"/>
+        <v>1.2564102564102626</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>10009662</v>
+      </c>
+      <c r="B34" s="4">
+        <v>114</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="0"/>
+        <v>12.027027027027032</v>
+      </c>
+      <c r="E34" s="3">
+        <v>10009662</v>
+      </c>
+      <c r="F34" s="4">
+        <v>105</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="1"/>
+        <v>23.78378378378379</v>
+      </c>
+      <c r="I34" s="3">
+        <v>10009662</v>
+      </c>
+      <c r="J34" s="4">
+        <v>75</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="2"/>
+        <v>3.5</v>
+      </c>
+      <c r="M34" s="3">
+        <v>10009662</v>
+      </c>
+      <c r="N34" s="4">
+        <v>82</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="3"/>
+        <v>17.717948717948715</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>10009662</v>
+      </c>
+      <c r="R34" s="4">
+        <v>134</v>
+      </c>
+      <c r="S34">
+        <f t="shared" si="4"/>
+        <v>49.743589743589737</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>10011641</v>
+      </c>
+      <c r="B35" s="4">
+        <v>110</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="0"/>
+        <v>8.0270270270270316</v>
+      </c>
+      <c r="E35" s="3">
+        <v>10011641</v>
+      </c>
+      <c r="F35" s="4">
+        <v>92</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="1"/>
+        <v>10.78378378378379</v>
+      </c>
+      <c r="I35" s="3">
+        <v>10011641</v>
+      </c>
+      <c r="J35" s="4">
+        <v>123</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="2"/>
+        <v>44.5</v>
+      </c>
+      <c r="M35" s="3">
+        <v>10011641</v>
+      </c>
+      <c r="N35" s="4">
+        <v>141</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="3"/>
+        <v>41.282051282051285</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>10011641</v>
+      </c>
+      <c r="R35" s="4">
+        <v>74</v>
+      </c>
+      <c r="S35">
+        <f t="shared" si="4"/>
+        <v>10.256410256410263</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>10014010</v>
+      </c>
+      <c r="B36" s="4">
+        <v>103</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="0"/>
+        <v>1.0270270270270316</v>
+      </c>
+      <c r="E36" s="3">
+        <v>10014010</v>
+      </c>
+      <c r="F36" s="4">
+        <v>100</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="1"/>
+        <v>18.78378378378379</v>
+      </c>
+      <c r="I36" s="3">
+        <v>10014010</v>
+      </c>
+      <c r="J36" s="4">
+        <v>87</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="2"/>
+        <v>8.5</v>
+      </c>
+      <c r="M36" s="3">
+        <v>10014010</v>
+      </c>
+      <c r="N36" s="4">
+        <v>85</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="3"/>
+        <v>14.717948717948715</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>10014010</v>
+      </c>
+      <c r="R36" s="4">
+        <v>81</v>
+      </c>
+      <c r="S36">
+        <f t="shared" si="4"/>
+        <v>3.2564102564102626</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>10014255</v>
+      </c>
+      <c r="B37" s="4">
+        <v>121</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="0"/>
+        <v>19.027027027027032</v>
+      </c>
+      <c r="E37" s="3">
+        <v>10014255</v>
+      </c>
+      <c r="F37" s="4">
+        <v>88</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="1"/>
+        <v>6.7837837837837895</v>
+      </c>
+      <c r="I37" s="3">
+        <v>10014255</v>
+      </c>
+      <c r="J37" s="4">
+        <v>95</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="2"/>
+        <v>16.5</v>
+      </c>
+      <c r="M37" s="3">
+        <v>10014255</v>
+      </c>
+      <c r="N37" s="4">
+        <v>132</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="3"/>
+        <v>32.282051282051285</v>
+      </c>
+      <c r="Q37" s="3">
+        <v>10014255</v>
+      </c>
+      <c r="R37" s="4">
+        <v>82</v>
+      </c>
+      <c r="S37">
+        <f t="shared" si="4"/>
+        <v>2.2564102564102626</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>10014704</v>
+      </c>
+      <c r="B38" s="4">
+        <v>97</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="0"/>
+        <v>4.9729729729729684</v>
+      </c>
+      <c r="E38" s="3">
+        <v>10014704</v>
+      </c>
+      <c r="F38" s="4">
+        <v>108</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="1"/>
+        <v>26.78378378378379</v>
+      </c>
+      <c r="I38" s="3">
+        <v>10014704</v>
+      </c>
+      <c r="J38" s="4">
+        <v>83</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="2"/>
+        <v>4.5</v>
+      </c>
+      <c r="M38" s="3">
+        <v>10014704</v>
+      </c>
+      <c r="N38" s="4">
+        <v>106</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="3"/>
+        <v>6.2820512820512846</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>10014704</v>
+      </c>
+      <c r="R38" s="4">
+        <v>90</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="4"/>
+        <v>5.7435897435897374</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>10024737</v>
+      </c>
+      <c r="B39" s="4">
+        <v>102</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="0"/>
+        <v>2.7027027027031636E-2</v>
+      </c>
+      <c r="E39" s="3">
+        <v>10024737</v>
+      </c>
+      <c r="F39" s="4">
+        <v>68</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="1"/>
+        <v>13.21621621621621</v>
+      </c>
+      <c r="I39" s="3">
+        <v>10024737</v>
+      </c>
+      <c r="J39" s="4">
+        <v>59</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="2"/>
+        <v>19.5</v>
+      </c>
+      <c r="M39" s="3">
+        <v>10024737</v>
+      </c>
+      <c r="N39" s="4">
+        <v>106</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="3"/>
+        <v>6.2820512820512846</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>10024737</v>
+      </c>
+      <c r="R39" s="4">
+        <v>96</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="4"/>
+        <v>11.743589743589737</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>10024880</v>
+      </c>
+      <c r="B40" s="4">
+        <v>120</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="0"/>
+        <v>18.027027027027032</v>
+      </c>
+      <c r="E40" s="3">
+        <v>10024880</v>
+      </c>
+      <c r="F40" s="4">
+        <v>112</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="1"/>
+        <v>30.78378378378379</v>
+      </c>
+      <c r="I40" s="3">
+        <v>10024880</v>
+      </c>
+      <c r="J40" s="4">
+        <v>82</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="2"/>
+        <v>3.5</v>
+      </c>
+      <c r="M40" s="3">
+        <v>10024880</v>
+      </c>
+      <c r="N40" s="4">
+        <v>100</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="3"/>
+        <v>0.2820512820512846</v>
+      </c>
+      <c r="Q40" s="3">
+        <v>10024880</v>
+      </c>
+      <c r="R40" s="4">
         <v>109</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="4">
+      <c r="S40">
+        <f t="shared" si="4"/>
+        <v>24.743589743589737</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>10025537</v>
+      </c>
+      <c r="B41" s="4">
+        <v>115</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="0"/>
+        <v>13.027027027027032</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10025537</v>
+      </c>
+      <c r="F41" s="4">
+        <v>89</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="1"/>
+        <v>7.7837837837837895</v>
+      </c>
+      <c r="I41" s="3">
+        <v>10025537</v>
+      </c>
+      <c r="J41" s="4">
+        <v>101</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="2"/>
+        <v>22.5</v>
+      </c>
+      <c r="M41" s="3">
+        <v>10025537</v>
+      </c>
+      <c r="N41" s="4">
+        <v>115</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="3"/>
+        <v>15.282051282051285</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>10025537</v>
+      </c>
+      <c r="R41" s="4">
+        <v>89</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="4"/>
+        <v>4.7435897435897374</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>10025538</v>
+      </c>
+      <c r="B42" s="4">
+        <v>119</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="0"/>
+        <v>17.027027027027032</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10025538</v>
+      </c>
+      <c r="F42" s="4">
+        <v>73</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="1"/>
+        <v>8.2162162162162105</v>
+      </c>
+      <c r="I42" s="3">
+        <v>10025538</v>
+      </c>
+      <c r="J42" s="4">
+        <v>72</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="2"/>
+        <v>6.5</v>
+      </c>
+      <c r="M42" s="3">
+        <v>10025538</v>
+      </c>
+      <c r="N42" s="4">
+        <v>85</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="3"/>
+        <v>14.717948717948715</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>10025538</v>
+      </c>
+      <c r="R42" s="4">
+        <v>94</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="4"/>
+        <v>9.7435897435897374</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>10029570</v>
+      </c>
+      <c r="B43" s="4">
+        <v>123</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="0"/>
+        <v>21.027027027027032</v>
+      </c>
+      <c r="E43" s="3">
+        <v>10029570</v>
+      </c>
+      <c r="F43" s="4">
+        <v>107</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="1"/>
+        <v>25.78378378378379</v>
+      </c>
+      <c r="I43" s="3">
+        <v>10029570</v>
+      </c>
+      <c r="J43" s="4">
+        <v>86</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="2"/>
+        <v>7.5</v>
+      </c>
+      <c r="M43" s="3">
+        <v>10029570</v>
+      </c>
+      <c r="N43" s="4">
+        <v>106</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="3"/>
+        <v>6.2820512820512846</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>10029570</v>
+      </c>
+      <c r="R43" s="4">
+        <v>89</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="4"/>
+        <v>4.7435897435897374</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>10031843</v>
+      </c>
+      <c r="B44" s="4">
+        <v>90</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="0"/>
+        <v>11.972972972972968</v>
+      </c>
+      <c r="E44" s="3">
+        <v>10031843</v>
+      </c>
+      <c r="F44" s="4">
+        <v>71</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="1"/>
+        <v>10.21621621621621</v>
+      </c>
+      <c r="I44" s="3">
+        <v>10031843</v>
+      </c>
+      <c r="J44" s="4">
+        <v>88</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="2"/>
+        <v>9.5</v>
+      </c>
+      <c r="M44" s="3">
+        <v>10031843</v>
+      </c>
+      <c r="N44" s="4">
+        <v>124</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="3"/>
+        <v>24.282051282051285</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>10031843</v>
+      </c>
+      <c r="R44" s="4">
+        <v>74</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="4"/>
+        <v>10.256410256410263</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>10031844</v>
+      </c>
+      <c r="B45" s="4">
+        <v>55</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="0"/>
+        <v>46.972972972972968</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10031844</v>
+      </c>
+      <c r="F45" s="4">
+        <v>69</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="1"/>
+        <v>12.21621621621621</v>
+      </c>
+      <c r="I45" s="3">
+        <v>10031844</v>
+      </c>
+      <c r="J45" s="4">
+        <v>80</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="M45" s="3">
+        <v>10031844</v>
+      </c>
+      <c r="N45" s="4">
+        <v>97</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="3"/>
+        <v>2.7179487179487154</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>10031844</v>
+      </c>
+      <c r="R45" s="4">
+        <v>70</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="4"/>
+        <v>14.256410256410263</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>10031845</v>
+      </c>
+      <c r="B46" s="4">
+        <v>148</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="0"/>
+        <v>46.027027027027032</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10031845</v>
+      </c>
+      <c r="F46" s="4">
+        <v>101</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="1"/>
+        <v>19.78378378378379</v>
+      </c>
+      <c r="I46" s="3">
+        <v>10031845</v>
+      </c>
+      <c r="J46" s="4">
+        <v>80</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="M46" s="3">
+        <v>10031845</v>
+      </c>
+      <c r="N46" s="4">
+        <v>94</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="3"/>
+        <v>5.7179487179487154</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>10031845</v>
+      </c>
+      <c r="R46" s="4">
+        <v>94</v>
+      </c>
+      <c r="S46">
+        <f t="shared" si="4"/>
+        <v>9.7435897435897374</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>10035125</v>
+      </c>
+      <c r="B47" s="4">
+        <v>122</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="0"/>
+        <v>20.027027027027032</v>
+      </c>
+      <c r="E47" s="3">
+        <v>10035125</v>
+      </c>
+      <c r="F47" s="4">
+        <v>73</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="1"/>
+        <v>8.2162162162162105</v>
+      </c>
+      <c r="I47" s="3">
+        <v>10035125</v>
+      </c>
+      <c r="J47" s="4">
+        <v>106</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="2"/>
+        <v>27.5</v>
+      </c>
+      <c r="M47" s="3">
+        <v>10035125</v>
+      </c>
+      <c r="N47" s="4">
+        <v>125</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="3"/>
+        <v>25.282051282051285</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>10035125</v>
+      </c>
+      <c r="R47" s="4">
+        <v>102</v>
+      </c>
+      <c r="S47">
+        <f t="shared" si="4"/>
+        <v>17.743589743589737</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>10038027</v>
+      </c>
+      <c r="B48" s="4">
+        <v>159</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="0"/>
+        <v>57.027027027027032</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10038027</v>
+      </c>
+      <c r="F48" s="4">
+        <v>119</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="1"/>
+        <v>37.78378378378379</v>
+      </c>
+      <c r="I48" s="3">
+        <v>10038027</v>
+      </c>
+      <c r="J48" s="4">
+        <v>92</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="2"/>
+        <v>13.5</v>
+      </c>
+      <c r="M48" s="3">
+        <v>10038027</v>
+      </c>
+      <c r="N48" s="4">
+        <v>141</v>
+      </c>
+      <c r="O48">
+        <f t="shared" si="3"/>
+        <v>41.282051282051285</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>10038027</v>
+      </c>
+      <c r="R48" s="4">
+        <v>110</v>
+      </c>
+      <c r="S48">
+        <f t="shared" si="4"/>
+        <v>25.743589743589737</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>10046352</v>
+      </c>
+      <c r="B49" s="4">
+        <v>44</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="0"/>
+        <v>57.972972972972968</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10046352</v>
+      </c>
+      <c r="F49" s="4">
+        <v>52</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="1"/>
+        <v>29.21621621621621</v>
+      </c>
+      <c r="I49" s="3">
+        <v>10046352</v>
+      </c>
+      <c r="J49" s="4">
+        <v>65</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="2"/>
+        <v>13.5</v>
+      </c>
+      <c r="M49" s="3">
+        <v>10046352</v>
+      </c>
+      <c r="N49" s="4">
+        <v>76</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="3"/>
+        <v>23.717948717948715</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>10046352</v>
+      </c>
+      <c r="R49" s="4">
+        <v>67</v>
+      </c>
+      <c r="S49">
+        <f t="shared" si="4"/>
+        <v>17.256410256410263</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>10046795</v>
+      </c>
+      <c r="B50" s="4">
+        <v>125</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="0"/>
+        <v>23.027027027027032</v>
+      </c>
+      <c r="E50" s="3">
+        <v>10046795</v>
+      </c>
+      <c r="F50" s="4">
+        <v>78</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="1"/>
+        <v>3.2162162162162105</v>
+      </c>
+      <c r="I50" s="3">
+        <v>10046795</v>
+      </c>
+      <c r="J50" s="4">
+        <v>84</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="2"/>
+        <v>5.5</v>
+      </c>
+      <c r="M50" s="3">
+        <v>10046795</v>
+      </c>
+      <c r="N50" s="4">
+        <v>138</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="3"/>
+        <v>38.282051282051285</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>10046795</v>
+      </c>
+      <c r="R50" s="4">
+        <v>95</v>
+      </c>
+      <c r="S50">
+        <f t="shared" si="4"/>
+        <v>10.743589743589737</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>10047909</v>
+      </c>
+      <c r="B51" s="4">
+        <v>104</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="0"/>
+        <v>2.0270270270270316</v>
+      </c>
+      <c r="E51" s="3">
+        <v>10047909</v>
+      </c>
+      <c r="F51" s="4">
+        <v>73</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="1"/>
+        <v>8.2162162162162105</v>
+      </c>
+      <c r="I51" s="3">
+        <v>10047909</v>
+      </c>
+      <c r="J51" s="4">
+        <v>90</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="2"/>
+        <v>11.5</v>
+      </c>
+      <c r="M51" s="3">
+        <v>10047909</v>
+      </c>
+      <c r="N51" s="4">
+        <v>106</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="3"/>
+        <v>6.2820512820512846</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>10047909</v>
+      </c>
+      <c r="R51" s="4">
+        <v>65</v>
+      </c>
+      <c r="S51">
+        <f t="shared" si="4"/>
+        <v>19.256410256410263</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>10052254</v>
+      </c>
+      <c r="B52" s="4">
+        <v>113</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="0"/>
+        <v>11.027027027027032</v>
+      </c>
+      <c r="E52" s="3">
+        <v>10052254</v>
+      </c>
+      <c r="F52" s="4">
+        <v>90</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="1"/>
+        <v>8.7837837837837895</v>
+      </c>
+      <c r="I52" s="3">
+        <v>10052254</v>
+      </c>
+      <c r="J52" s="4">
+        <v>56</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="2"/>
+        <v>22.5</v>
+      </c>
+      <c r="M52" s="3">
+        <v>10052254</v>
+      </c>
+      <c r="N52" s="4">
+        <v>129</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="3"/>
+        <v>29.282051282051285</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>10052254</v>
+      </c>
+      <c r="R52" s="4">
+        <v>61</v>
+      </c>
+      <c r="S52">
+        <f t="shared" si="4"/>
+        <v>23.256410256410263</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>10053112</v>
+      </c>
+      <c r="B53" s="4">
+        <v>104</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="0"/>
+        <v>2.0270270270270316</v>
+      </c>
+      <c r="E53" s="3">
+        <v>10053112</v>
+      </c>
+      <c r="F53" s="4">
+        <v>91</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="1"/>
+        <v>9.7837837837837895</v>
+      </c>
+      <c r="I53" s="3">
+        <v>10053112</v>
+      </c>
+      <c r="J53" s="4">
+        <v>97</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="2"/>
+        <v>18.5</v>
+      </c>
+      <c r="M53" s="3">
+        <v>10053112</v>
+      </c>
+      <c r="N53" s="4">
+        <v>98</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="3"/>
+        <v>1.7179487179487154</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>10053112</v>
+      </c>
+      <c r="R53" s="4">
+        <v>77</v>
+      </c>
+      <c r="S53">
+        <f t="shared" si="4"/>
+        <v>7.2564102564102626</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>10055658</v>
+      </c>
+      <c r="B54" s="4">
+        <v>127</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="0"/>
+        <v>25.027027027027032</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10055658</v>
+      </c>
+      <c r="F54" s="4">
+        <v>85</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="1"/>
+        <v>3.7837837837837895</v>
+      </c>
+      <c r="I54" s="3">
+        <v>10055658</v>
+      </c>
+      <c r="J54" s="4">
+        <v>79</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="M54" s="3">
+        <v>10055658</v>
+      </c>
+      <c r="N54" s="4">
+        <v>122</v>
+      </c>
+      <c r="O54">
+        <f t="shared" si="3"/>
+        <v>22.282051282051285</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>10055658</v>
+      </c>
+      <c r="R54" s="4">
+        <v>66</v>
+      </c>
+      <c r="S54">
+        <f t="shared" si="4"/>
+        <v>18.256410256410263</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>10062125</v>
+      </c>
+      <c r="B55" s="4">
+        <v>112</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="0"/>
+        <v>10.027027027027032</v>
+      </c>
+      <c r="E55" s="3">
+        <v>10062125</v>
+      </c>
+      <c r="F55" s="4">
+        <v>113</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="1"/>
+        <v>31.78378378378379</v>
+      </c>
+      <c r="I55" s="3">
+        <v>10062125</v>
+      </c>
+      <c r="J55" s="4">
+        <v>102</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="2"/>
+        <v>23.5</v>
+      </c>
+      <c r="M55" s="3">
+        <v>10062125</v>
+      </c>
+      <c r="N55" s="4">
+        <v>135</v>
+      </c>
+      <c r="O55">
+        <f t="shared" si="3"/>
+        <v>35.282051282051285</v>
+      </c>
+      <c r="Q55" s="3">
+        <v>10062125</v>
+      </c>
+      <c r="R55" s="4">
+        <v>118</v>
+      </c>
+      <c r="S55">
+        <f t="shared" si="4"/>
+        <v>33.743589743589737</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>10064690</v>
+      </c>
+      <c r="B56" s="4">
+        <v>96</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="0"/>
+        <v>5.9729729729729684</v>
+      </c>
+      <c r="E56" s="3">
+        <v>10064690</v>
+      </c>
+      <c r="F56" s="4">
+        <v>63</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="1"/>
+        <v>18.21621621621621</v>
+      </c>
+      <c r="I56" s="3">
+        <v>10064690</v>
+      </c>
+      <c r="J56" s="4">
+        <v>63</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="2"/>
+        <v>15.5</v>
+      </c>
+      <c r="M56" s="3">
+        <v>10064690</v>
+      </c>
+      <c r="N56" s="4">
+        <v>72</v>
+      </c>
+      <c r="O56">
+        <f t="shared" si="3"/>
+        <v>27.717948717948715</v>
+      </c>
+      <c r="Q56" s="3">
+        <v>10064690</v>
+      </c>
+      <c r="R56" s="4">
+        <v>78</v>
+      </c>
+      <c r="S56">
+        <f t="shared" si="4"/>
+        <v>6.2564102564102626</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
+        <v>10068449</v>
+      </c>
+      <c r="B57" s="4">
+        <v>125</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="0"/>
+        <v>23.027027027027032</v>
+      </c>
+      <c r="E57" s="3">
+        <v>10068449</v>
+      </c>
+      <c r="F57" s="4">
+        <v>83</v>
+      </c>
+      <c r="G57">
+        <f t="shared" si="1"/>
+        <v>1.7837837837837895</v>
+      </c>
+      <c r="I57" s="3">
+        <v>10068449</v>
+      </c>
+      <c r="J57" s="4">
+        <v>91</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="2"/>
+        <v>12.5</v>
+      </c>
+      <c r="M57" s="3">
+        <v>10068449</v>
+      </c>
+      <c r="N57" s="4">
+        <v>125</v>
+      </c>
+      <c r="O57">
+        <f t="shared" si="3"/>
+        <v>25.282051282051285</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>10068449</v>
+      </c>
+      <c r="R57" s="4">
+        <v>97</v>
+      </c>
+      <c r="S57">
+        <f t="shared" si="4"/>
+        <v>12.743589743589737</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
+        <v>10072594</v>
+      </c>
+      <c r="B58" s="4">
+        <v>96</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="0"/>
+        <v>5.9729729729729684</v>
+      </c>
+      <c r="E58" s="3">
+        <v>10072594</v>
+      </c>
+      <c r="F58" s="4">
+        <v>76</v>
+      </c>
+      <c r="G58">
+        <f t="shared" si="1"/>
+        <v>5.2162162162162105</v>
+      </c>
+      <c r="I58" s="3">
+        <v>10072594</v>
+      </c>
+      <c r="J58" s="4">
+        <v>64</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="2"/>
+        <v>14.5</v>
+      </c>
+      <c r="M58" s="3">
+        <v>10072594</v>
+      </c>
+      <c r="N58" s="4">
+        <v>97</v>
+      </c>
+      <c r="O58">
+        <f t="shared" si="3"/>
+        <v>2.7179487179487154</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>10072594</v>
+      </c>
+      <c r="R58" s="4">
+        <v>86</v>
+      </c>
+      <c r="S58">
+        <f t="shared" si="4"/>
+        <v>1.7435897435897374</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
+        <v>10072947</v>
+      </c>
+      <c r="B59" s="4">
+        <v>87</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="0"/>
+        <v>14.972972972972968</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10072947</v>
+      </c>
+      <c r="F59" s="4">
+        <v>63</v>
+      </c>
+      <c r="G59">
+        <f t="shared" si="1"/>
+        <v>18.21621621621621</v>
+      </c>
+      <c r="I59" s="3">
+        <v>10072947</v>
+      </c>
+      <c r="J59" s="4">
+        <v>56</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="2"/>
+        <v>22.5</v>
+      </c>
+      <c r="M59" s="3">
+        <v>10072947</v>
+      </c>
+      <c r="N59" s="4">
+        <v>87</v>
+      </c>
+      <c r="O59">
+        <f t="shared" si="3"/>
+        <v>12.717948717948715</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>10072947</v>
+      </c>
+      <c r="R59" s="4">
+        <v>97</v>
+      </c>
+      <c r="S59">
+        <f t="shared" si="4"/>
+        <v>12.743589743589737</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
+        <v>10073889</v>
+      </c>
+      <c r="B60" s="4">
+        <v>109</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="0"/>
+        <v>7.0270270270270316</v>
+      </c>
+      <c r="E60" s="3">
+        <v>10074145</v>
+      </c>
+      <c r="F60" s="4">
+        <v>64</v>
+      </c>
+      <c r="G60">
+        <f t="shared" si="1"/>
+        <v>17.21621621621621</v>
+      </c>
+      <c r="I60" s="3">
+        <v>10073494</v>
+      </c>
+      <c r="J60" s="4">
+        <v>72</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="2"/>
+        <v>6.5</v>
+      </c>
+      <c r="M60" s="3">
+        <v>10073889</v>
+      </c>
+      <c r="N60" s="4">
+        <v>95</v>
+      </c>
+      <c r="O60">
+        <f t="shared" si="3"/>
+        <v>4.7179487179487154</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>10073494</v>
+      </c>
+      <c r="R60" s="4">
+        <v>80</v>
+      </c>
+      <c r="S60">
+        <f t="shared" si="4"/>
+        <v>4.2564102564102626</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <v>10074145</v>
+      </c>
+      <c r="B61" s="4">
+        <v>95</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="0"/>
+        <v>6.9729729729729684</v>
+      </c>
+      <c r="E61" s="3">
+        <v>10076349</v>
+      </c>
+      <c r="F61" s="4">
+        <v>59</v>
+      </c>
+      <c r="G61">
+        <f t="shared" si="1"/>
+        <v>22.21621621621621</v>
+      </c>
+      <c r="I61" s="3">
+        <v>10073889</v>
+      </c>
+      <c r="J61" s="4">
+        <v>77</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="M61" s="3">
+        <v>10074145</v>
+      </c>
+      <c r="N61" s="4">
+        <v>92</v>
+      </c>
+      <c r="O61">
+        <f t="shared" si="3"/>
+        <v>7.7179487179487154</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>10073889</v>
+      </c>
+      <c r="R61" s="4">
+        <v>80</v>
+      </c>
+      <c r="S61">
+        <f t="shared" si="4"/>
+        <v>4.2564102564102626</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <v>10076349</v>
+      </c>
+      <c r="B62" s="4">
+        <v>93</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="0"/>
+        <v>8.9729729729729684</v>
+      </c>
+      <c r="E62" s="3">
+        <v>10078132</v>
+      </c>
+      <c r="F62" s="4">
+        <v>101</v>
+      </c>
+      <c r="G62">
+        <f t="shared" si="1"/>
+        <v>19.78378378378379</v>
+      </c>
+      <c r="I62" s="3">
+        <v>10074145</v>
+      </c>
+      <c r="J62" s="4">
+        <v>90</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="2"/>
+        <v>11.5</v>
+      </c>
+      <c r="M62" s="3">
+        <v>10076349</v>
+      </c>
+      <c r="N62" s="4">
+        <v>73</v>
+      </c>
+      <c r="O62">
+        <f t="shared" si="3"/>
+        <v>26.717948717948715</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>10074145</v>
+      </c>
+      <c r="R62" s="4">
+        <v>87</v>
+      </c>
+      <c r="S62">
+        <f t="shared" si="4"/>
+        <v>2.7435897435897374</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
+        <v>10078132</v>
+      </c>
+      <c r="B63" s="4">
+        <v>107</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="0"/>
+        <v>5.0270270270270316</v>
+      </c>
+      <c r="E63" s="3">
+        <v>10079995</v>
+      </c>
+      <c r="F63" s="4">
+        <v>70</v>
+      </c>
+      <c r="G63">
+        <f t="shared" si="1"/>
+        <v>11.21621621621621</v>
+      </c>
+      <c r="I63" s="3">
+        <v>10076349</v>
+      </c>
+      <c r="J63" s="4">
+        <v>80</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="M63" s="3">
+        <v>10078132</v>
+      </c>
+      <c r="N63" s="4">
+        <v>93</v>
+      </c>
+      <c r="O63">
+        <f t="shared" si="3"/>
+        <v>6.7179487179487154</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>10076349</v>
+      </c>
+      <c r="R63" s="4">
+        <v>88</v>
+      </c>
+      <c r="S63">
+        <f t="shared" si="4"/>
+        <v>3.7435897435897374</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <v>10079995</v>
+      </c>
+      <c r="B64" s="4">
+        <v>103</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="0"/>
+        <v>1.0270270270270316</v>
+      </c>
+      <c r="E64" s="3">
+        <v>10080481</v>
+      </c>
+      <c r="F64" s="4">
+        <v>40</v>
+      </c>
+      <c r="G64">
+        <f t="shared" si="1"/>
+        <v>41.21621621621621</v>
+      </c>
+      <c r="I64" s="3">
+        <v>10078132</v>
+      </c>
+      <c r="J64" s="4">
+        <v>93</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="2"/>
+        <v>14.5</v>
+      </c>
+      <c r="M64" s="3">
+        <v>10079995</v>
+      </c>
+      <c r="N64" s="4">
+        <v>88</v>
+      </c>
+      <c r="O64">
+        <f t="shared" si="3"/>
+        <v>11.717948717948715</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>10078132</v>
+      </c>
+      <c r="R64" s="4">
+        <v>80</v>
+      </c>
+      <c r="S64">
+        <f t="shared" si="4"/>
+        <v>4.2564102564102626</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <v>10080481</v>
+      </c>
+      <c r="B65" s="4">
+        <v>61</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="0"/>
+        <v>40.972972972972968</v>
+      </c>
+      <c r="E65" s="3">
+        <v>10080492</v>
+      </c>
+      <c r="F65" s="4">
+        <v>74</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="1"/>
+        <v>7.2162162162162105</v>
+      </c>
+      <c r="I65" s="3">
+        <v>10079995</v>
+      </c>
+      <c r="J65" s="4">
+        <v>67</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="2"/>
+        <v>11.5</v>
+      </c>
+      <c r="M65" s="3">
+        <v>10080481</v>
+      </c>
+      <c r="N65" s="4">
+        <v>73</v>
+      </c>
+      <c r="O65">
+        <f t="shared" si="3"/>
+        <v>26.717948717948715</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>10079995</v>
+      </c>
+      <c r="R65" s="4">
+        <v>60</v>
+      </c>
+      <c r="S65">
+        <f t="shared" si="4"/>
+        <v>24.256410256410263</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <v>10080492</v>
+      </c>
+      <c r="B66" s="4">
+        <v>47</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="0"/>
+        <v>54.972972972972968</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10080526</v>
+      </c>
+      <c r="F66" s="4">
+        <v>35</v>
+      </c>
+      <c r="G66">
+        <f t="shared" si="1"/>
+        <v>46.21621621621621</v>
+      </c>
+      <c r="I66" s="3">
+        <v>10080481</v>
+      </c>
+      <c r="J66" s="4">
+        <v>55</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="2"/>
+        <v>23.5</v>
+      </c>
+      <c r="M66" s="3">
+        <v>10080492</v>
+      </c>
+      <c r="N66" s="4">
+        <v>69</v>
+      </c>
+      <c r="O66">
+        <f t="shared" si="3"/>
+        <v>30.717948717948715</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>10080481</v>
+      </c>
+      <c r="R66" s="4">
+        <v>67</v>
+      </c>
+      <c r="S66">
+        <f t="shared" si="4"/>
+        <v>17.256410256410263</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <v>10080526</v>
+      </c>
+      <c r="B67" s="4">
+        <v>26</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="0"/>
+        <v>75.972972972972968</v>
+      </c>
+      <c r="E67" s="3">
+        <v>10080596</v>
+      </c>
+      <c r="F67" s="4">
+        <v>52</v>
+      </c>
+      <c r="G67">
+        <f t="shared" si="1"/>
+        <v>29.21621621621621</v>
+      </c>
+      <c r="I67" s="3">
+        <v>10080492</v>
+      </c>
+      <c r="J67" s="4">
+        <v>59</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="2"/>
+        <v>19.5</v>
+      </c>
+      <c r="M67" s="3">
+        <v>10080596</v>
+      </c>
+      <c r="N67" s="4">
+        <v>75</v>
+      </c>
+      <c r="O67">
+        <f t="shared" si="3"/>
+        <v>24.717948717948715</v>
+      </c>
+      <c r="Q67" s="3">
+        <v>10080492</v>
+      </c>
+      <c r="R67" s="4">
+        <v>68</v>
+      </c>
+      <c r="S67">
+        <f t="shared" si="4"/>
+        <v>16.256410256410263</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="10">
+        <f>AVERAGE(B31:B67)</f>
+        <v>101.97297297297297</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F68" s="10">
+        <f>AVERAGE(F31:F67)</f>
+        <v>81.21621621621621</v>
+      </c>
+      <c r="I68" s="3">
+        <v>10080596</v>
+      </c>
+      <c r="J68" s="4">
+        <v>56</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="2"/>
+        <v>22.5</v>
+      </c>
+      <c r="M68" s="3">
+        <v>10080624</v>
+      </c>
+      <c r="N68" s="4">
+        <v>47</v>
+      </c>
+      <c r="O68">
+        <f t="shared" si="3"/>
+        <v>52.717948717948715</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>10080596</v>
+      </c>
+      <c r="R68" s="4">
+        <v>51</v>
+      </c>
+      <c r="S68">
+        <f t="shared" si="4"/>
+        <v>33.256410256410263</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="4">
-        <v>2749</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="4">
-        <v>37</v>
-      </c>
-      <c r="C25" s="4">
-        <v>2718</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="4">
+      <c r="B69" s="10">
+        <f>STDEVA(B31:B67)</f>
+        <v>27.329762456265797</v>
+      </c>
+      <c r="E69" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="4">
-        <v>3286</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="F69" s="10">
+        <f>STDEVA(F31:F67)</f>
+        <v>20.534706576286258</v>
+      </c>
+      <c r="I69" s="3">
+        <v>10080624</v>
+      </c>
+      <c r="J69" s="4">
+        <v>41</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="2"/>
+        <v>37.5</v>
+      </c>
+      <c r="M69" s="3">
+        <v>10080747</v>
+      </c>
+      <c r="N69" s="4">
+        <v>39</v>
+      </c>
+      <c r="O69">
+        <f t="shared" si="3"/>
+        <v>60.717948717948715</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>10080747</v>
+      </c>
+      <c r="R69" s="4">
+        <v>62</v>
+      </c>
+      <c r="S69">
+        <f t="shared" si="4"/>
+        <v>22.256410256410263</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B70" s="10">
+        <f>SUM(C31:C67)/COUNT(A31:A67)</f>
+        <v>19.384952520087651</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F70" s="10">
+        <f>SUM(G31:G67)/COUNT(E31:E67)</f>
+        <v>16.762600438276117</v>
+      </c>
+      <c r="I70" s="3">
+        <v>10080747</v>
+      </c>
+      <c r="J70" s="4">
         <v>28</v>
       </c>
-      <c r="B27" s="4">
-        <v>647</v>
-      </c>
-      <c r="C27" s="4">
-        <v>33729</v>
+      <c r="K70">
+        <f t="shared" si="2"/>
+        <v>50.5</v>
+      </c>
+      <c r="M70" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N70" s="10">
+        <f>AVERAGE(N31:N69)</f>
+        <v>99.717948717948715</v>
+      </c>
+      <c r="Q70" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="R70" s="10">
+        <f>AVERAGE(R31:R69)</f>
+        <v>84.256410256410263</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I71" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J71" s="10">
+        <f>AVERAGE(J31:J70)</f>
+        <v>78.5</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N71" s="10">
+        <f>STDEVA(N31:N69)</f>
+        <v>24.888116714131833</v>
+      </c>
+      <c r="Q71" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R71" s="10">
+        <f>STDEVA(R31:R69)</f>
+        <v>17.187385136409201</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I72" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J72" s="10">
+        <f>STDEVA(J31:J70)</f>
+        <v>18.91546647045406</v>
+      </c>
+      <c r="M72" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="N72" s="10">
+        <f>SUM(O31:O69)/COUNT(M31:M69)</f>
+        <v>19.952662721893493</v>
+      </c>
+      <c r="Q72" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="R72" s="10">
+        <f>SUM(S31:S69)/COUNT(Q31:Q69)</f>
+        <v>13.301775147928996</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I73" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J73" s="10">
+        <f>SUM(K31:K70)/COUNT(I31:I70)</f>
+        <v>14.925000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -14867,4 +17644,3188 @@
   <autoFilter ref="A1:D648" xr:uid="{66C4AC6B-552E-471F-9EAB-C16AFC013511}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEEDBC97-83BF-473C-9ED6-9E9D09C223F1}">
+  <dimension ref="A3:G45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>10074145</v>
+      </c>
+      <c r="B4" s="4">
+        <v>19</v>
+      </c>
+      <c r="C4" s="4">
+        <v>824</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1138.5311440688481</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4">
+        <f>AVERAGE(D4:D44)</f>
+        <v>463.02053115896717</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>10053112</v>
+      </c>
+      <c r="B5" s="4">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4">
+        <v>944</v>
+      </c>
+      <c r="D5" s="4">
+        <v>830.89388482273898</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>10035125</v>
+      </c>
+      <c r="B6" s="4">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1078</v>
+      </c>
+      <c r="D6" s="4">
+        <v>685.17578694000531</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>10080492</v>
+      </c>
+      <c r="B7" s="4">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4">
+        <v>644</v>
+      </c>
+      <c r="D7" s="4">
+        <v>677.42722417322159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>10014010</v>
+      </c>
+      <c r="B8" s="4">
+        <v>17</v>
+      </c>
+      <c r="C8" s="4">
+        <v>965</v>
+      </c>
+      <c r="D8" s="4">
+        <v>674.74857312562904</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>10055658</v>
+      </c>
+      <c r="B9" s="4">
+        <v>17</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1087</v>
+      </c>
+      <c r="D9" s="4">
+        <v>579.88402414992947</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>10047909</v>
+      </c>
+      <c r="B10" s="4">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4">
+        <v>874</v>
+      </c>
+      <c r="D10" s="4">
+        <v>577.06195207205838</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>10003936</v>
+      </c>
+      <c r="B11" s="4">
+        <v>17</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1058</v>
+      </c>
+      <c r="D11" s="4">
+        <v>548.77185908791364</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>10025537</v>
+      </c>
+      <c r="B12" s="4">
+        <v>17</v>
+      </c>
+      <c r="C12" s="4">
+        <v>964</v>
+      </c>
+      <c r="D12" s="4">
+        <v>533.39929235040756</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>10062125</v>
+      </c>
+      <c r="B13" s="4">
+        <v>18</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1215</v>
+      </c>
+      <c r="D13" s="4">
+        <v>532.44432505522786</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>10068449</v>
+      </c>
+      <c r="B14" s="4">
+        <v>17</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1097</v>
+      </c>
+      <c r="D14" s="4">
+        <v>527.98415406592778</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>10031845</v>
+      </c>
+      <c r="B15" s="4">
+        <v>15</v>
+      </c>
+      <c r="C15" s="4">
+        <v>818</v>
+      </c>
+      <c r="D15" s="4">
+        <v>517.27020254185572</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>10038027</v>
+      </c>
+      <c r="B16" s="4">
+        <v>16</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1075</v>
+      </c>
+      <c r="D16" s="4">
+        <v>513.38591052848267</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>10024737</v>
+      </c>
+      <c r="B17" s="4">
+        <v>17</v>
+      </c>
+      <c r="C17" s="4">
+        <v>973</v>
+      </c>
+      <c r="D17" s="4">
+        <v>507.78080929216867</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>10024880</v>
+      </c>
+      <c r="B18" s="4">
+        <v>16</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1054</v>
+      </c>
+      <c r="D18" s="4">
+        <v>503.5859470233342</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>10079995</v>
+      </c>
+      <c r="B19" s="4">
+        <v>17</v>
+      </c>
+      <c r="C19" s="4">
+        <v>785</v>
+      </c>
+      <c r="D19" s="4">
+        <v>502.18220534542974</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>10046795</v>
+      </c>
+      <c r="B20" s="4">
+        <v>17</v>
+      </c>
+      <c r="C20" s="4">
+        <v>991</v>
+      </c>
+      <c r="D20" s="4">
+        <v>477.57049284952905</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>10064690</v>
+      </c>
+      <c r="B21" s="4">
+        <v>18</v>
+      </c>
+      <c r="C21" s="4">
+        <v>737</v>
+      </c>
+      <c r="D21" s="4">
+        <v>476.64115217340657</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>10014704</v>
+      </c>
+      <c r="B22" s="4">
+        <v>16</v>
+      </c>
+      <c r="C22" s="4">
+        <v>929</v>
+      </c>
+      <c r="D22" s="4">
+        <v>471.12254618230116</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>10001245</v>
+      </c>
+      <c r="B23" s="4">
+        <v>17</v>
+      </c>
+      <c r="C23" s="4">
+        <v>863</v>
+      </c>
+      <c r="D23" s="4">
+        <v>467.60127816058917</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>10011641</v>
+      </c>
+      <c r="B24" s="4">
+        <v>18</v>
+      </c>
+      <c r="C24" s="4">
+        <v>977</v>
+      </c>
+      <c r="D24" s="4">
+        <v>463.85368450106949</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>10031844</v>
+      </c>
+      <c r="B25" s="4">
+        <v>17</v>
+      </c>
+      <c r="C25" s="4">
+        <v>715</v>
+      </c>
+      <c r="D25" s="4">
+        <v>461.80807612739619</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>10006503</v>
+      </c>
+      <c r="B26" s="4">
+        <v>17</v>
+      </c>
+      <c r="C26" s="4">
+        <v>975</v>
+      </c>
+      <c r="D26" s="4">
+        <v>453.92259755301927</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>10014255</v>
+      </c>
+      <c r="B27" s="4">
+        <v>16</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1013</v>
+      </c>
+      <c r="D27" s="4">
+        <v>451.08950831208591</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>10078132</v>
+      </c>
+      <c r="B28" s="4">
+        <v>18</v>
+      </c>
+      <c r="C28" s="4">
+        <v>957</v>
+      </c>
+      <c r="D28" s="4">
+        <v>425.20801889729626</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>10072947</v>
+      </c>
+      <c r="B29" s="4">
+        <v>16</v>
+      </c>
+      <c r="C29" s="4">
+        <v>805</v>
+      </c>
+      <c r="D29" s="4">
+        <v>418.90482802917762</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>10029570</v>
+      </c>
+      <c r="B30" s="4">
+        <v>16</v>
+      </c>
+      <c r="C30" s="4">
+        <v>1007</v>
+      </c>
+      <c r="D30" s="4">
+        <v>418.30785318939013</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>10072594</v>
+      </c>
+      <c r="B31" s="4">
+        <v>17</v>
+      </c>
+      <c r="C31" s="4">
+        <v>789</v>
+      </c>
+      <c r="D31" s="4">
+        <v>417.14019327926013</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>10080481</v>
+      </c>
+      <c r="B32" s="4">
+        <v>17</v>
+      </c>
+      <c r="C32" s="4">
+        <v>603</v>
+      </c>
+      <c r="D32" s="4">
+        <v>415.03376896121887</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>10025538</v>
+      </c>
+      <c r="B33" s="4">
+        <v>16</v>
+      </c>
+      <c r="C33" s="4">
+        <v>803</v>
+      </c>
+      <c r="D33" s="4">
+        <v>404.60756680505193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>10031843</v>
+      </c>
+      <c r="B34" s="4">
+        <v>17</v>
+      </c>
+      <c r="C34" s="4">
+        <v>802</v>
+      </c>
+      <c r="D34" s="4">
+        <v>403.27583716541915</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>10052254</v>
+      </c>
+      <c r="B35" s="4">
+        <v>15</v>
+      </c>
+      <c r="C35" s="4">
+        <v>766</v>
+      </c>
+      <c r="D35" s="4">
+        <v>387.27744420315918</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>10073889</v>
+      </c>
+      <c r="B36" s="4">
+        <v>15</v>
+      </c>
+      <c r="C36" s="4">
+        <v>708</v>
+      </c>
+      <c r="D36" s="4">
+        <v>380.55131070778793</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>10076349</v>
+      </c>
+      <c r="B37" s="4">
+        <v>18</v>
+      </c>
+      <c r="C37" s="4">
+        <v>800</v>
+      </c>
+      <c r="D37" s="4">
+        <v>366.46647639493449</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>10009662</v>
+      </c>
+      <c r="B38" s="4">
+        <v>17</v>
+      </c>
+      <c r="C38" s="4">
+        <v>982</v>
+      </c>
+      <c r="D38" s="4">
+        <v>363.52175631590325</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>10080596</v>
+      </c>
+      <c r="B39" s="4">
+        <v>12</v>
+      </c>
+      <c r="C39" s="4">
+        <v>414</v>
+      </c>
+      <c r="D39" s="4">
+        <v>283.24603271438605</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>10073494</v>
+      </c>
+      <c r="B40" s="4">
+        <v>13</v>
+      </c>
+      <c r="C40" s="4">
+        <v>588</v>
+      </c>
+      <c r="D40" s="4">
+        <v>239.05656298426646</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>10046352</v>
+      </c>
+      <c r="B41" s="4">
+        <v>15</v>
+      </c>
+      <c r="C41" s="4">
+        <v>542</v>
+      </c>
+      <c r="D41" s="4">
+        <v>225.80996102190471</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>10080747</v>
+      </c>
+      <c r="B42" s="4">
+        <v>7</v>
+      </c>
+      <c r="C42" s="4">
+        <v>252</v>
+      </c>
+      <c r="D42" s="4">
+        <v>127.36792410229592</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>10080624</v>
+      </c>
+      <c r="B43" s="4">
+        <v>7</v>
+      </c>
+      <c r="C43" s="4">
+        <v>160</v>
+      </c>
+      <c r="D43" s="4">
+        <v>78.465934254304287</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>10080526</v>
+      </c>
+      <c r="B44" s="4">
+        <v>7</v>
+      </c>
+      <c r="C44" s="4">
+        <v>96</v>
+      </c>
+      <c r="D44" s="4">
+        <v>55.463677989325248</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" s="4">
+        <v>647</v>
+      </c>
+      <c r="C45" s="4">
+        <v>33729</v>
+      </c>
+      <c r="D45" s="4">
+        <v>18983.841777517657</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32721555-190E-4D4B-A02C-A04E7E5B225F}">
+  <dimension ref="A2:S73"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="12">
+        <f>(B70+F70+J73+N72+R72)/5</f>
+        <v>12.096084811088611</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2.8650753483456879</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4">
+        <v>33</v>
+      </c>
+      <c r="C4" s="4">
+        <v>103</v>
+      </c>
+      <c r="D4" s="4">
+        <v>3.9593215387067451</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4">
+        <v>35</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1243</v>
+      </c>
+      <c r="D5" s="4">
+        <v>23.859197406172427</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4">
+        <v>33</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2649</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46.414215339600659</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="8">
+        <v>37</v>
+      </c>
+      <c r="C7" s="8">
+        <v>3773</v>
+      </c>
+      <c r="D7" s="8">
+        <v>50.419868716772477</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="8">
+        <v>37</v>
+      </c>
+      <c r="C8" s="8">
+        <v>3005</v>
+      </c>
+      <c r="D8" s="8">
+        <v>44.762473658203021</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="4">
+        <v>39</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2272</v>
+      </c>
+      <c r="D9" s="4">
+        <v>33.085821379379027</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4">
+        <v>40</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1012</v>
+      </c>
+      <c r="D10" s="4">
+        <v>15.885232193425619</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2.6539806782346749</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="4">
+        <v>3</v>
+      </c>
+      <c r="C12" s="4">
+        <v>3</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1.6229573812050735</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4">
+        <v>40</v>
+      </c>
+      <c r="C13" s="4">
+        <v>279</v>
+      </c>
+      <c r="D13" s="4">
+        <v>6.8353126501307218</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4">
+        <v>38</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1821</v>
+      </c>
+      <c r="D14" s="4">
+        <v>29.39627924808423</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="8">
+        <v>40</v>
+      </c>
+      <c r="C15" s="8">
+        <v>3140</v>
+      </c>
+      <c r="D15" s="8">
+        <v>38.506714860538501</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8">
+        <v>39</v>
+      </c>
+      <c r="C16" s="8">
+        <v>3889</v>
+      </c>
+      <c r="D16" s="8">
+        <v>54.384789219770795</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4">
+        <v>39</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1394</v>
+      </c>
+      <c r="D17" s="4">
+        <v>21.800645018658727</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4">
+        <v>39</v>
+      </c>
+      <c r="C18" s="4">
+        <v>277</v>
+      </c>
+      <c r="D18" s="4">
+        <v>6.3458594779350532</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4">
+        <v>3.4545051302870071</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.43429804578488568</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="4">
+        <v>2</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2</v>
+      </c>
+      <c r="D21" s="4">
+        <v>2.7939449756182539</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="4">
+        <v>33</v>
+      </c>
+      <c r="C22" s="4">
+        <v>109</v>
+      </c>
+      <c r="D22" s="4">
+        <v>4.3579814490127369</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="4">
+        <v>39</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2749</v>
+      </c>
+      <c r="D23" s="4">
+        <v>36.95963924079836</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="4">
+        <v>37</v>
+      </c>
+      <c r="C24" s="4">
+        <v>2718</v>
+      </c>
+      <c r="D24" s="4">
+        <v>42.16288013995419</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="8">
+        <v>39</v>
+      </c>
+      <c r="C25" s="8">
+        <v>3286</v>
+      </c>
+      <c r="D25" s="8">
+        <v>44.140626027837882</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="4">
+        <v>647</v>
+      </c>
+      <c r="C26" s="4">
+        <v>33729</v>
+      </c>
+      <c r="D26" s="4">
+        <v>29.341331959069016</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A29" s="9">
+        <v>46231</v>
+      </c>
+      <c r="E29" s="9">
+        <v>46232</v>
+      </c>
+      <c r="I29" s="9">
+        <v>46240</v>
+      </c>
+      <c r="M29" s="9">
+        <v>46241</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="R30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S30" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>10001245</v>
+      </c>
+      <c r="B31">
+        <v>67.949704105988062</v>
+      </c>
+      <c r="C31">
+        <f>ABS(B31-$B$68)</f>
+        <v>17.529835389215584</v>
+      </c>
+      <c r="E31">
+        <v>10001245</v>
+      </c>
+      <c r="F31">
+        <v>37.432457027880858</v>
+      </c>
+      <c r="G31">
+        <f>ABS(F31-$F$68)</f>
+        <v>7.330016630322163</v>
+      </c>
+      <c r="I31">
+        <v>10001245</v>
+      </c>
+      <c r="J31">
+        <v>31.518555038529222</v>
+      </c>
+      <c r="K31">
+        <f>ABS(J31-$J$71)</f>
+        <v>6.9881598220092798</v>
+      </c>
+      <c r="M31">
+        <v>10001245</v>
+      </c>
+      <c r="N31">
+        <v>47.337889181157742</v>
+      </c>
+      <c r="O31">
+        <f>ABS(N31-$N$70)</f>
+        <v>7.0469000386130531</v>
+      </c>
+      <c r="Q31">
+        <v>10001245</v>
+      </c>
+      <c r="R31">
+        <v>34.479814157908798</v>
+      </c>
+      <c r="S31">
+        <f>ABS(R31-$R$70)</f>
+        <v>9.6608118699290841</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>10003936</v>
+      </c>
+      <c r="B32">
+        <v>49.891531295963993</v>
+      </c>
+      <c r="C32">
+        <f t="shared" ref="C32:C67" si="0">ABS(B32-$B$68)</f>
+        <v>0.52833742080848367</v>
+      </c>
+      <c r="E32">
+        <v>10003936</v>
+      </c>
+      <c r="F32">
+        <v>52.568307567947834</v>
+      </c>
+      <c r="G32">
+        <f t="shared" ref="G32:G67" si="1">ABS(F32-$F$68)</f>
+        <v>7.8058339097448126</v>
+      </c>
+      <c r="I32">
+        <v>10003936</v>
+      </c>
+      <c r="J32">
+        <v>41.07973683690718</v>
+      </c>
+      <c r="K32">
+        <f t="shared" ref="K32:K70" si="2">ABS(J32-$J$71)</f>
+        <v>2.573021976368679</v>
+      </c>
+      <c r="M32">
+        <v>10003936</v>
+      </c>
+      <c r="N32">
+        <v>68.774795601024906</v>
+      </c>
+      <c r="O32">
+        <f t="shared" ref="O32:O69" si="3">ABS(N32-$N$70)</f>
+        <v>14.390006381254111</v>
+      </c>
+      <c r="Q32">
+        <v>10003936</v>
+      </c>
+      <c r="R32">
+        <v>57.236973884026753</v>
+      </c>
+      <c r="S32">
+        <f t="shared" ref="S32:S69" si="4">ABS(R32-$R$70)</f>
+        <v>13.096347856188871</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>10006503</v>
+      </c>
+      <c r="B33">
+        <v>38.346146260469013</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="0"/>
+        <v>12.073722456303464</v>
+      </c>
+      <c r="E33">
+        <v>10006503</v>
+      </c>
+      <c r="F33">
+        <v>45.78334586746363</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="1"/>
+        <v>1.0208722092606095</v>
+      </c>
+      <c r="I33">
+        <v>10006503</v>
+      </c>
+      <c r="J33">
+        <v>33.983399069124218</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="2"/>
+        <v>4.5233157914142836</v>
+      </c>
+      <c r="M33">
+        <v>10006503</v>
+      </c>
+      <c r="N33">
+        <v>47.543383181283261</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="3"/>
+        <v>6.8414060384875341</v>
+      </c>
+      <c r="Q33">
+        <v>10006503</v>
+      </c>
+      <c r="R33">
+        <v>38.534244830769133</v>
+      </c>
+      <c r="S33">
+        <f t="shared" si="4"/>
+        <v>5.6063811970687496</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>10009662</v>
+      </c>
+      <c r="B34">
+        <v>40.536307869471628</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="0"/>
+        <v>9.8835608473008492</v>
+      </c>
+      <c r="E34">
+        <v>10009662</v>
+      </c>
+      <c r="F34">
+        <v>35.297528428997268</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="1"/>
+        <v>9.4649452292057532</v>
+      </c>
+      <c r="I34">
+        <v>10009662</v>
+      </c>
+      <c r="J34">
+        <v>30.77391842487485</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="2"/>
+        <v>7.7327964356636514</v>
+      </c>
+      <c r="M34">
+        <v>10009662</v>
+      </c>
+      <c r="N34">
+        <v>26.54948623448567</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="3"/>
+        <v>27.835302985285125</v>
+      </c>
+      <c r="Q34">
+        <v>10009662</v>
+      </c>
+      <c r="R34">
+        <v>47.235444642767888</v>
+      </c>
+      <c r="S34">
+        <f t="shared" si="4"/>
+        <v>3.0948186149300057</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>10011641</v>
+      </c>
+      <c r="B35">
+        <v>50.055675771382958</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="0"/>
+        <v>0.36419294538951874</v>
+      </c>
+      <c r="E35">
+        <v>10011641</v>
+      </c>
+      <c r="F35">
+        <v>37.948472252952897</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="1"/>
+        <v>6.8140014052501243</v>
+      </c>
+      <c r="I35">
+        <v>10011641</v>
+      </c>
+      <c r="J35">
+        <v>41.595331209499513</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="2"/>
+        <v>3.0886163489610112</v>
+      </c>
+      <c r="M35">
+        <v>10011641</v>
+      </c>
+      <c r="N35">
+        <v>74.736096911784458</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="3"/>
+        <v>20.351307692013663</v>
+      </c>
+      <c r="Q35">
+        <v>10011641</v>
+      </c>
+      <c r="R35">
+        <v>37.161174145237602</v>
+      </c>
+      <c r="S35">
+        <f t="shared" si="4"/>
+        <v>6.97945188260028</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>10014010</v>
+      </c>
+      <c r="B36">
+        <v>85.193885257684229</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="0"/>
+        <v>34.774016540911752</v>
+      </c>
+      <c r="E36">
+        <v>10014010</v>
+      </c>
+      <c r="F36">
+        <v>70.407870491246612</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="1"/>
+        <v>25.645396833043591</v>
+      </c>
+      <c r="I36">
+        <v>10014010</v>
+      </c>
+      <c r="J36">
+        <v>44.004867674138787</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="2"/>
+        <v>5.4981528136002851</v>
+      </c>
+      <c r="M36">
+        <v>10014010</v>
+      </c>
+      <c r="N36">
+        <v>48.826201875820878</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="3"/>
+        <v>5.5585873439499167</v>
+      </c>
+      <c r="Q36">
+        <v>10014010</v>
+      </c>
+      <c r="R36">
+        <v>56.330518869662207</v>
+      </c>
+      <c r="S36">
+        <f t="shared" si="4"/>
+        <v>12.189892841824324</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>10014255</v>
+      </c>
+      <c r="B37">
+        <v>50.779446424757857</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="0"/>
+        <v>0.35957770798538036</v>
+      </c>
+      <c r="E37">
+        <v>10014255</v>
+      </c>
+      <c r="F37">
+        <v>35.398292618470059</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="1"/>
+        <v>9.3641810397329621</v>
+      </c>
+      <c r="I37">
+        <v>10014255</v>
+      </c>
+      <c r="J37">
+        <v>37.306381660639893</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="2"/>
+        <v>1.2003331998986084</v>
+      </c>
+      <c r="M37">
+        <v>10014255</v>
+      </c>
+      <c r="N37">
+        <v>46.437192079308957</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="3"/>
+        <v>7.9475971404618377</v>
+      </c>
+      <c r="Q37">
+        <v>10014255</v>
+      </c>
+      <c r="R37">
+        <v>36.312287946839078</v>
+      </c>
+      <c r="S37">
+        <f t="shared" si="4"/>
+        <v>7.8283380809988046</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>10014704</v>
+      </c>
+      <c r="B38">
+        <v>39.65373177788377</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="0"/>
+        <v>10.766136938888707</v>
+      </c>
+      <c r="E38">
+        <v>10014704</v>
+      </c>
+      <c r="F38">
+        <v>55.240894475948792</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="1"/>
+        <v>10.478420817745771</v>
+      </c>
+      <c r="I38">
+        <v>10014704</v>
+      </c>
+      <c r="J38">
+        <v>43.712586713400263</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="2"/>
+        <v>5.2058718528617618</v>
+      </c>
+      <c r="M38">
+        <v>10014704</v>
+      </c>
+      <c r="N38">
+        <v>57.747643627027742</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="3"/>
+        <v>3.3628544072569468</v>
+      </c>
+      <c r="Q38">
+        <v>10014704</v>
+      </c>
+      <c r="R38">
+        <v>37.33179042130449</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="4"/>
+        <v>6.8088356065333926</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>10024737</v>
+      </c>
+      <c r="B39">
+        <v>52.583117394984932</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="0"/>
+        <v>2.1632486782124545</v>
+      </c>
+      <c r="E39">
+        <v>10024737</v>
+      </c>
+      <c r="F39">
+        <v>28.137474566738849</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="1"/>
+        <v>16.624999091464172</v>
+      </c>
+      <c r="I39">
+        <v>10024737</v>
+      </c>
+      <c r="J39">
+        <v>29.37356640435285</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="2"/>
+        <v>9.1331484561856513</v>
+      </c>
+      <c r="M39">
+        <v>10024737</v>
+      </c>
+      <c r="N39">
+        <v>35.933201216429687</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="3"/>
+        <v>18.451588003341108</v>
+      </c>
+      <c r="Q39">
+        <v>10024737</v>
+      </c>
+      <c r="R39">
+        <v>41.648881594027017</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="4"/>
+        <v>2.4917444338108652</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>10024880</v>
+      </c>
+      <c r="B40">
+        <v>47.697762819118942</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="0"/>
+        <v>2.7221058976535346</v>
+      </c>
+      <c r="E40">
+        <v>10024880</v>
+      </c>
+      <c r="F40">
+        <v>47.091762759721178</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="1"/>
+        <v>2.3292891015181567</v>
+      </c>
+      <c r="I40">
+        <v>10024880</v>
+      </c>
+      <c r="J40">
+        <v>29.12679465437521</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="2"/>
+        <v>9.3799202061632911</v>
+      </c>
+      <c r="M40">
+        <v>10024880</v>
+      </c>
+      <c r="N40">
+        <v>39.355258184927393</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="3"/>
+        <v>15.029531034843401</v>
+      </c>
+      <c r="Q40">
+        <v>10024880</v>
+      </c>
+      <c r="R40">
+        <v>49.956264783839117</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="4"/>
+        <v>5.8156387560012348</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>10025537</v>
+      </c>
+      <c r="B41">
+        <v>60.830976044197961</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="0"/>
+        <v>10.411107327425484</v>
+      </c>
+      <c r="E41">
+        <v>10025537</v>
+      </c>
+      <c r="F41">
+        <v>48.872337749533919</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="1"/>
+        <v>4.1098640913308984</v>
+      </c>
+      <c r="I41">
+        <v>10025537</v>
+      </c>
+      <c r="J41">
+        <v>50.947864144898347</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="2"/>
+        <v>12.441149284359845</v>
+      </c>
+      <c r="M41">
+        <v>10025537</v>
+      </c>
+      <c r="N41">
+        <v>49.419741779866627</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="3"/>
+        <v>4.9650474399041684</v>
+      </c>
+      <c r="Q41">
+        <v>10025537</v>
+      </c>
+      <c r="R41">
+        <v>57.110430061385173</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="4"/>
+        <v>12.969804033547291</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>10025538</v>
+      </c>
+      <c r="B42">
+        <v>50.788681135826458</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="0"/>
+        <v>0.36881241905398099</v>
+      </c>
+      <c r="E42">
+        <v>10025538</v>
+      </c>
+      <c r="F42">
+        <v>32.269782886426107</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="1"/>
+        <v>12.492690771776914</v>
+      </c>
+      <c r="I42">
+        <v>10025538</v>
+      </c>
+      <c r="J42">
+        <v>40.331323298435628</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="2"/>
+        <v>1.8246084378971261</v>
+      </c>
+      <c r="M42">
+        <v>10025538</v>
+      </c>
+      <c r="N42">
+        <v>50.768607430101021</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="3"/>
+        <v>3.6161817896697741</v>
+      </c>
+      <c r="Q42">
+        <v>10025538</v>
+      </c>
+      <c r="R42">
+        <v>42.522048396619518</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="4"/>
+        <v>1.6185776312183648</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>10029570</v>
+      </c>
+      <c r="B43">
+        <v>38.238734127440992</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="0"/>
+        <v>12.181134589331485</v>
+      </c>
+      <c r="E43">
+        <v>10029570</v>
+      </c>
+      <c r="F43">
+        <v>43.535038426554067</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="1"/>
+        <v>1.2274352316489541</v>
+      </c>
+      <c r="I43">
+        <v>10029570</v>
+      </c>
+      <c r="J43">
+        <v>32.700367669198073</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="2"/>
+        <v>5.8063471913404285</v>
+      </c>
+      <c r="M43">
+        <v>10029570</v>
+      </c>
+      <c r="N43">
+        <v>34.949929932550752</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="3"/>
+        <v>19.434859287220043</v>
+      </c>
+      <c r="Q43">
+        <v>10029570</v>
+      </c>
+      <c r="R43">
+        <v>48.239941572300182</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="4"/>
+        <v>4.0993155444623</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>10031843</v>
+      </c>
+      <c r="B44">
+        <v>36.730866819068467</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="0"/>
+        <v>13.68900189770401</v>
+      </c>
+      <c r="E44">
+        <v>10031843</v>
+      </c>
+      <c r="F44">
+        <v>30.91460930029988</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="1"/>
+        <v>13.847864357903141</v>
+      </c>
+      <c r="I44">
+        <v>10031843</v>
+      </c>
+      <c r="J44">
+        <v>37.983639333749842</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="2"/>
+        <v>0.52307552678865932</v>
+      </c>
+      <c r="M44">
+        <v>10031843</v>
+      </c>
+      <c r="N44">
+        <v>55.087239609654013</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="3"/>
+        <v>0.70245038988321795</v>
+      </c>
+      <c r="Q44">
+        <v>10031843</v>
+      </c>
+      <c r="R44">
+        <v>39.774309091171013</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="4"/>
+        <v>4.3663169366668697</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>10031844</v>
+      </c>
+      <c r="B45">
+        <v>42.400824314017747</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="0"/>
+        <v>8.0190444027547301</v>
+      </c>
+      <c r="E45">
+        <v>10031844</v>
+      </c>
+      <c r="F45">
+        <v>45.596808797731242</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="1"/>
+        <v>0.83433513952822125</v>
+      </c>
+      <c r="I45">
+        <v>10031844</v>
+      </c>
+      <c r="J45">
+        <v>30.67307899420658</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="2"/>
+        <v>7.833635866331921</v>
+      </c>
+      <c r="M45">
+        <v>10031844</v>
+      </c>
+      <c r="N45">
+        <v>65.63992696692253</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="3"/>
+        <v>11.255137747151736</v>
+      </c>
+      <c r="Q45">
+        <v>10031844</v>
+      </c>
+      <c r="R45">
+        <v>44.935369993312243</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="4"/>
+        <v>0.79474396547436044</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>10031845</v>
+      </c>
+      <c r="B46">
+        <v>61.435985131423152</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="0"/>
+        <v>11.016116414650675</v>
+      </c>
+      <c r="E46">
+        <v>10031845</v>
+      </c>
+      <c r="F46">
+        <v>67.163754693836268</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="1"/>
+        <v>22.401281035633247</v>
+      </c>
+      <c r="I46">
+        <v>10031845</v>
+      </c>
+      <c r="J46">
+        <v>46.589337015989933</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="2"/>
+        <v>8.0826221554514319</v>
+      </c>
+      <c r="M46">
+        <v>10031845</v>
+      </c>
+      <c r="N46">
+        <v>74.029842915224762</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="3"/>
+        <v>19.645053695453967</v>
+      </c>
+      <c r="Q46">
+        <v>10031845</v>
+      </c>
+      <c r="R46">
+        <v>65.935517866145261</v>
+      </c>
+      <c r="S46">
+        <f t="shared" si="4"/>
+        <v>21.794891838307379</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>10035125</v>
+      </c>
+      <c r="B47">
+        <v>64.792192432035478</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="0"/>
+        <v>14.372323715263001</v>
+      </c>
+      <c r="E47">
+        <v>10035125</v>
+      </c>
+      <c r="F47">
+        <v>40.576884092877947</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="1"/>
+        <v>4.1855895653250741</v>
+      </c>
+      <c r="I47">
+        <v>10035125</v>
+      </c>
+      <c r="J47">
+        <v>51.711779098193119</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="2"/>
+        <v>13.205064237654618</v>
+      </c>
+      <c r="M47">
+        <v>10035125</v>
+      </c>
+      <c r="N47">
+        <v>88.319142419177766</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="3"/>
+        <v>33.934353199406971</v>
+      </c>
+      <c r="Q47">
+        <v>10035125</v>
+      </c>
+      <c r="R47">
+        <v>62.472312387850529</v>
+      </c>
+      <c r="S47">
+        <f t="shared" si="4"/>
+        <v>18.331686360012647</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>10038027</v>
+      </c>
+      <c r="B48">
+        <v>56.634620329455167</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="0"/>
+        <v>6.2147516126826901</v>
+      </c>
+      <c r="E48">
+        <v>10038027</v>
+      </c>
+      <c r="F48">
+        <v>56.495568431995032</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="1"/>
+        <v>11.733094773792011</v>
+      </c>
+      <c r="I48">
+        <v>10038027</v>
+      </c>
+      <c r="J48">
+        <v>38.592559819771068</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="2"/>
+        <v>8.5844959232566964E-2</v>
+      </c>
+      <c r="M48">
+        <v>10038027</v>
+      </c>
+      <c r="N48">
+        <v>51.246057683441343</v>
+      </c>
+      <c r="O48">
+        <f t="shared" si="3"/>
+        <v>3.1387315363294519</v>
+      </c>
+      <c r="Q48">
+        <v>10038027</v>
+      </c>
+      <c r="R48">
+        <v>43.057943254102362</v>
+      </c>
+      <c r="S48">
+        <f t="shared" si="4"/>
+        <v>1.0826827737355202</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>10046352</v>
+      </c>
+      <c r="B49">
+        <v>18.425747915945351</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="0"/>
+        <v>31.994120800827126</v>
+      </c>
+      <c r="E49">
+        <v>10046352</v>
+      </c>
+      <c r="F49">
+        <v>17.70980704606011</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="1"/>
+        <v>27.052666612142911</v>
+      </c>
+      <c r="I49">
+        <v>10046352</v>
+      </c>
+      <c r="J49">
+        <v>21.4469109694016</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="2"/>
+        <v>17.059803891136902</v>
+      </c>
+      <c r="M49">
+        <v>10046352</v>
+      </c>
+      <c r="N49">
+        <v>26.669772001695431</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="3"/>
+        <v>27.715017218075364</v>
+      </c>
+      <c r="Q49">
+        <v>10046352</v>
+      </c>
+      <c r="R49">
+        <v>26.41742460598865</v>
+      </c>
+      <c r="S49">
+        <f t="shared" si="4"/>
+        <v>17.723201421849232</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>10046795</v>
+      </c>
+      <c r="B50">
+        <v>57.906262416186593</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="0"/>
+        <v>7.4863936994141156</v>
+      </c>
+      <c r="E50">
+        <v>10046795</v>
+      </c>
+      <c r="F50">
+        <v>35.455788969635023</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="1"/>
+        <v>9.3066846885679979</v>
+      </c>
+      <c r="I50">
+        <v>10046795</v>
+      </c>
+      <c r="J50">
+        <v>32.83093749740496</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="2"/>
+        <v>5.6757773631335411</v>
+      </c>
+      <c r="M50">
+        <v>10046795</v>
+      </c>
+      <c r="N50">
+        <v>53.744394639411603</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="3"/>
+        <v>0.64039458035919239</v>
+      </c>
+      <c r="Q50">
+        <v>10046795</v>
+      </c>
+      <c r="R50">
+        <v>47.433083636996379</v>
+      </c>
+      <c r="S50">
+        <f t="shared" si="4"/>
+        <v>3.2924576091584967</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>10047909</v>
+      </c>
+      <c r="B51">
+        <v>55.656750594574497</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="0"/>
+        <v>5.2368818778020199</v>
+      </c>
+      <c r="E51">
+        <v>10047909</v>
+      </c>
+      <c r="F51">
+        <v>37.625800767456212</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="1"/>
+        <v>7.1366728907468087</v>
+      </c>
+      <c r="I51">
+        <v>10047909</v>
+      </c>
+      <c r="J51">
+        <v>47.421984079246258</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="2"/>
+        <v>8.9152692187077562</v>
+      </c>
+      <c r="M51">
+        <v>10047909</v>
+      </c>
+      <c r="N51">
+        <v>56.763575874455299</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="3"/>
+        <v>2.3787866546845038</v>
+      </c>
+      <c r="Q51">
+        <v>10047909</v>
+      </c>
+      <c r="R51">
+        <v>42.515238211613998</v>
+      </c>
+      <c r="S51">
+        <f t="shared" si="4"/>
+        <v>1.6253878162238848</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>10052254</v>
+      </c>
+      <c r="B52">
+        <v>51.599639378526959</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="0"/>
+        <v>1.1797706617544819</v>
+      </c>
+      <c r="E52">
+        <v>10052254</v>
+      </c>
+      <c r="F52">
+        <v>44.703701286369188</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="1"/>
+        <v>5.8772371833832437E-2</v>
+      </c>
+      <c r="I52">
+        <v>10052254</v>
+      </c>
+      <c r="J52">
+        <v>22.508605287024722</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="2"/>
+        <v>15.99810957351378</v>
+      </c>
+      <c r="M52">
+        <v>10052254</v>
+      </c>
+      <c r="N52">
+        <v>79.203436661984412</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="3"/>
+        <v>24.818647442213617</v>
+      </c>
+      <c r="Q52">
+        <v>10052254</v>
+      </c>
+      <c r="R52">
+        <v>24.55429070829662</v>
+      </c>
+      <c r="S52">
+        <f t="shared" si="4"/>
+        <v>19.586335319541263</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>10053112</v>
+      </c>
+      <c r="B53">
+        <v>72.518330380932667</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="0"/>
+        <v>22.09846166416019</v>
+      </c>
+      <c r="E53">
+        <v>10053112</v>
+      </c>
+      <c r="F53">
+        <v>60.890674466453177</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="1"/>
+        <v>16.128200808250156</v>
+      </c>
+      <c r="I53">
+        <v>10053112</v>
+      </c>
+      <c r="J53">
+        <v>84.341150779535283</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="2"/>
+        <v>45.834435918996782</v>
+      </c>
+      <c r="M53">
+        <v>10053112</v>
+      </c>
+      <c r="N53">
+        <v>67.007507764046125</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="3"/>
+        <v>12.62271854427533</v>
+      </c>
+      <c r="Q53">
+        <v>10053112</v>
+      </c>
+      <c r="R53">
+        <v>92.322403072655277</v>
+      </c>
+      <c r="S53">
+        <f t="shared" si="4"/>
+        <v>48.181777044817395</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>10055658</v>
+      </c>
+      <c r="B54">
+        <v>53.93246206468087</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="0"/>
+        <v>3.5125933479083926</v>
+      </c>
+      <c r="E54">
+        <v>10055658</v>
+      </c>
+      <c r="F54">
+        <v>60.531198988795239</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="1"/>
+        <v>15.768725330592218</v>
+      </c>
+      <c r="I54">
+        <v>10055658</v>
+      </c>
+      <c r="J54">
+        <v>34.84816121090342</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="2"/>
+        <v>3.6585536496350812</v>
+      </c>
+      <c r="M54">
+        <v>10055658</v>
+      </c>
+      <c r="N54">
+        <v>58.498033591265781</v>
+      </c>
+      <c r="O54">
+        <f t="shared" si="3"/>
+        <v>4.1132443714949858</v>
+      </c>
+      <c r="Q54">
+        <v>10055658</v>
+      </c>
+      <c r="R54">
+        <v>32.994765958644038</v>
+      </c>
+      <c r="S54">
+        <f t="shared" si="4"/>
+        <v>11.145860069193844</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>10062125</v>
+      </c>
+      <c r="B55">
+        <v>55.729383411793883</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="0"/>
+        <v>5.3095146950214058</v>
+      </c>
+      <c r="E55">
+        <v>10062125</v>
+      </c>
+      <c r="F55">
+        <v>54.501152138372802</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="1"/>
+        <v>9.7386784801697814</v>
+      </c>
+      <c r="I55">
+        <v>10062125</v>
+      </c>
+      <c r="J55">
+        <v>37.958829078323809</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="2"/>
+        <v>0.54788578221469209</v>
+      </c>
+      <c r="M55">
+        <v>10062125</v>
+      </c>
+      <c r="N55">
+        <v>55.548203604142167</v>
+      </c>
+      <c r="O55">
+        <f t="shared" si="3"/>
+        <v>1.1634143843713716</v>
+      </c>
+      <c r="Q55">
+        <v>10062125</v>
+      </c>
+      <c r="R55">
+        <v>45.535644584807933</v>
+      </c>
+      <c r="S55">
+        <f t="shared" si="4"/>
+        <v>1.3950185569700508</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>10064690</v>
+      </c>
+      <c r="B56">
+        <v>40.219280725321752</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="0"/>
+        <v>10.200587991450725</v>
+      </c>
+      <c r="E56">
+        <v>10064690</v>
+      </c>
+      <c r="F56">
+        <v>47.239322318582467</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="1"/>
+        <v>2.4768486603794457</v>
+      </c>
+      <c r="I56">
+        <v>10064690</v>
+      </c>
+      <c r="J56">
+        <v>24.494198670053091</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="2"/>
+        <v>14.01251619048541</v>
+      </c>
+      <c r="M56">
+        <v>10064690</v>
+      </c>
+      <c r="N56">
+        <v>47.661427619515877</v>
+      </c>
+      <c r="O56">
+        <f t="shared" si="3"/>
+        <v>6.7233616002549184</v>
+      </c>
+      <c r="Q56">
+        <v>10064690</v>
+      </c>
+      <c r="R56">
+        <v>54.004923025103039</v>
+      </c>
+      <c r="S56">
+        <f t="shared" si="4"/>
+        <v>9.8642969972651571</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>10068449</v>
+      </c>
+      <c r="B57">
+        <v>52.282829952789783</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="0"/>
+        <v>1.8629612360173056</v>
+      </c>
+      <c r="E57">
+        <v>10068449</v>
+      </c>
+      <c r="F57">
+        <v>42.199333780347771</v>
+      </c>
+      <c r="G57">
+        <f t="shared" si="1"/>
+        <v>2.5631398778552494</v>
+      </c>
+      <c r="I57">
+        <v>10068449</v>
+      </c>
+      <c r="J57">
+        <v>52.330369022175027</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="2"/>
+        <v>13.823654161636526</v>
+      </c>
+      <c r="M57">
+        <v>10068449</v>
+      </c>
+      <c r="N57">
+        <v>51.662453335126983</v>
+      </c>
+      <c r="O57">
+        <f t="shared" si="3"/>
+        <v>2.7223358846438117</v>
+      </c>
+      <c r="Q57">
+        <v>10068449</v>
+      </c>
+      <c r="R57">
+        <v>33.550279475107217</v>
+      </c>
+      <c r="S57">
+        <f t="shared" si="4"/>
+        <v>10.590346552730665</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>10072594</v>
+      </c>
+      <c r="B58">
+        <v>50.645457641197751</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="0"/>
+        <v>0.22558892442527423</v>
+      </c>
+      <c r="E58">
+        <v>10072594</v>
+      </c>
+      <c r="F58">
+        <v>42.807948668882467</v>
+      </c>
+      <c r="G58">
+        <f t="shared" si="1"/>
+        <v>1.9545249893205536</v>
+      </c>
+      <c r="I58">
+        <v>10072594</v>
+      </c>
+      <c r="J58">
+        <v>27.139677491863988</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="2"/>
+        <v>11.367037368674513</v>
+      </c>
+      <c r="M58">
+        <v>10072594</v>
+      </c>
+      <c r="N58">
+        <v>50.512491248993577</v>
+      </c>
+      <c r="O58">
+        <f t="shared" si="3"/>
+        <v>3.8722979707772183</v>
+      </c>
+      <c r="Q58">
+        <v>10072594</v>
+      </c>
+      <c r="R58">
+        <v>36.749642815587038</v>
+      </c>
+      <c r="S58">
+        <f t="shared" si="4"/>
+        <v>7.3909832122508448</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>10072947</v>
+      </c>
+      <c r="B59">
+        <v>39.726645705859752</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="0"/>
+        <v>10.693223010912725</v>
+      </c>
+      <c r="E59">
+        <v>10072947</v>
+      </c>
+      <c r="F59">
+        <v>33.192844371952731</v>
+      </c>
+      <c r="G59">
+        <f t="shared" si="1"/>
+        <v>11.56962928625029</v>
+      </c>
+      <c r="I59">
+        <v>10072947</v>
+      </c>
+      <c r="J59">
+        <v>29.473567110492471</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="2"/>
+        <v>9.0331477500460302</v>
+      </c>
+      <c r="M59">
+        <v>10072947</v>
+      </c>
+      <c r="N59">
+        <v>45.707380727990952</v>
+      </c>
+      <c r="O59">
+        <f t="shared" si="3"/>
+        <v>8.6774084917798433</v>
+      </c>
+      <c r="Q59">
+        <v>10072947</v>
+      </c>
+      <c r="R59">
+        <v>39.012398801041229</v>
+      </c>
+      <c r="S59">
+        <f t="shared" si="4"/>
+        <v>5.1282272267966533</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>10073889</v>
+      </c>
+      <c r="B60">
+        <v>37.592084482094009</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="0"/>
+        <v>12.827784234678468</v>
+      </c>
+      <c r="E60">
+        <v>10074145</v>
+      </c>
+      <c r="F60">
+        <v>112.29568917838439</v>
+      </c>
+      <c r="G60">
+        <f t="shared" si="1"/>
+        <v>67.533215520181372</v>
+      </c>
+      <c r="I60">
+        <v>10073494</v>
+      </c>
+      <c r="J60">
+        <v>22.248803424616</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="2"/>
+        <v>16.257911435922502</v>
+      </c>
+      <c r="M60">
+        <v>10073889</v>
+      </c>
+      <c r="N60">
+        <v>55.633053677518447</v>
+      </c>
+      <c r="O60">
+        <f t="shared" si="3"/>
+        <v>1.248264457747652</v>
+      </c>
+      <c r="Q60">
+        <v>10073494</v>
+      </c>
+      <c r="R60">
+        <v>23.225137526873581</v>
+      </c>
+      <c r="S60">
+        <f t="shared" si="4"/>
+        <v>20.915488500964301</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>10074145</v>
+      </c>
+      <c r="B61">
+        <v>116.429554879983</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="0"/>
+        <v>66.009686163210517</v>
+      </c>
+      <c r="E61">
+        <v>10076349</v>
+      </c>
+      <c r="F61">
+        <v>22.332122929403141</v>
+      </c>
+      <c r="G61">
+        <f t="shared" si="1"/>
+        <v>22.43035072879988</v>
+      </c>
+      <c r="I61">
+        <v>10073889</v>
+      </c>
+      <c r="J61">
+        <v>35.434524084021938</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="2"/>
+        <v>3.0721907765165639</v>
+      </c>
+      <c r="M61">
+        <v>10074145</v>
+      </c>
+      <c r="N61">
+        <v>161.32818183571251</v>
+      </c>
+      <c r="O61">
+        <f t="shared" si="3"/>
+        <v>106.94339261594172</v>
+      </c>
+      <c r="Q61">
+        <v>10073889</v>
+      </c>
+      <c r="R61">
+        <v>31.97212982132627</v>
+      </c>
+      <c r="S61">
+        <f t="shared" si="4"/>
+        <v>12.168496206511612</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>10076349</v>
+      </c>
+      <c r="B62">
+        <v>42.4413626359188</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="0"/>
+        <v>7.978506080853677</v>
+      </c>
+      <c r="E62">
+        <v>10078132</v>
+      </c>
+      <c r="F62">
+        <v>50.1056341902257</v>
+      </c>
+      <c r="G62">
+        <f t="shared" si="1"/>
+        <v>5.3431605320226794</v>
+      </c>
+      <c r="I62">
+        <v>10074145</v>
+      </c>
+      <c r="J62">
+        <v>135.31051423773121</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="2"/>
+        <v>96.803799377192718</v>
+      </c>
+      <c r="M62">
+        <v>10076349</v>
+      </c>
+      <c r="N62">
+        <v>30.07402223525045</v>
+      </c>
+      <c r="O62">
+        <f t="shared" si="3"/>
+        <v>24.310766984520345</v>
+      </c>
+      <c r="Q62">
+        <v>10074145</v>
+      </c>
+      <c r="R62">
+        <v>44.856314305424569</v>
+      </c>
+      <c r="S62">
+        <f t="shared" si="4"/>
+        <v>0.71568827758668618</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>10078132</v>
+      </c>
+      <c r="B63">
+        <v>50.743800994464422</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="0"/>
+        <v>0.3239322776919451</v>
+      </c>
+      <c r="E63">
+        <v>10079995</v>
+      </c>
+      <c r="F63">
+        <v>53.625244918392617</v>
+      </c>
+      <c r="G63">
+        <f t="shared" si="1"/>
+        <v>8.8627712601895965</v>
+      </c>
+      <c r="I63">
+        <v>10076349</v>
+      </c>
+      <c r="J63">
+        <v>30.55096762807041</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="2"/>
+        <v>7.9557472324680916</v>
+      </c>
+      <c r="M63">
+        <v>10078132</v>
+      </c>
+      <c r="N63">
+        <v>34.985966861486162</v>
+      </c>
+      <c r="O63">
+        <f t="shared" si="3"/>
+        <v>19.398822358284633</v>
+      </c>
+      <c r="Q63">
+        <v>10076349</v>
+      </c>
+      <c r="R63">
+        <v>36.200312623362187</v>
+      </c>
+      <c r="S63">
+        <f t="shared" si="4"/>
+        <v>7.9403134044756953</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>10079995</v>
+      </c>
+      <c r="B64">
+        <v>56.324005072580448</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="0"/>
+        <v>5.9041363558079709</v>
+      </c>
+      <c r="E64">
+        <v>10080481</v>
+      </c>
+      <c r="F64">
+        <v>30.597354235063499</v>
+      </c>
+      <c r="G64">
+        <f t="shared" si="1"/>
+        <v>14.165119423139522</v>
+      </c>
+      <c r="I64">
+        <v>10078132</v>
+      </c>
+      <c r="J64">
+        <v>31.33381756568318</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="2"/>
+        <v>7.1728972948553213</v>
+      </c>
+      <c r="M64">
+        <v>10079995</v>
+      </c>
+      <c r="N64">
+        <v>54.089898978943161</v>
+      </c>
+      <c r="O64">
+        <f t="shared" si="3"/>
+        <v>0.29489024082763393</v>
+      </c>
+      <c r="Q64">
+        <v>10078132</v>
+      </c>
+      <c r="R64">
+        <v>40.019422049008341</v>
+      </c>
+      <c r="S64">
+        <f t="shared" si="4"/>
+        <v>4.1212039788295414</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>10080481</v>
+      </c>
+      <c r="B65">
+        <v>25.102402134086109</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="0"/>
+        <v>25.317466582686368</v>
+      </c>
+      <c r="E65">
+        <v>10080492</v>
+      </c>
+      <c r="F65">
+        <v>61.942440956861716</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="1"/>
+        <v>17.179967298658696</v>
+      </c>
+      <c r="I65">
+        <v>10079995</v>
+      </c>
+      <c r="J65">
+        <v>42.618058879297941</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="2"/>
+        <v>4.1113440187594392</v>
+      </c>
+      <c r="M65">
+        <v>10080481</v>
+      </c>
+      <c r="N65">
+        <v>53.738086507027433</v>
+      </c>
+      <c r="O65">
+        <f t="shared" si="3"/>
+        <v>0.64670271274336244</v>
+      </c>
+      <c r="Q65">
+        <v>10079995</v>
+      </c>
+      <c r="R65">
+        <v>25.83620714563267</v>
+      </c>
+      <c r="S65">
+        <f t="shared" si="4"/>
+        <v>18.304418882205212</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>10080492</v>
+      </c>
+      <c r="B66">
+        <v>41.7077946984571</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="0"/>
+        <v>8.7120740183153771</v>
+      </c>
+      <c r="E66">
+        <v>10080526</v>
+      </c>
+      <c r="F66">
+        <v>17.327094324329089</v>
+      </c>
+      <c r="G66">
+        <f t="shared" si="1"/>
+        <v>27.435379333873932</v>
+      </c>
+      <c r="I66">
+        <v>10080481</v>
+      </c>
+      <c r="J66">
+        <v>31.42914363857048</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="2"/>
+        <v>7.0775712219680216</v>
+      </c>
+      <c r="M66">
+        <v>10080492</v>
+      </c>
+      <c r="N66">
+        <v>81.959432855473437</v>
+      </c>
+      <c r="O66">
+        <f t="shared" si="3"/>
+        <v>27.574643635702643</v>
+      </c>
+      <c r="Q66">
+        <v>10080481</v>
+      </c>
+      <c r="R66">
+        <v>40.257092819678782</v>
+      </c>
+      <c r="S66">
+        <f t="shared" si="4"/>
+        <v>3.8835332081591005</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>10080526</v>
+      </c>
+      <c r="B67">
+        <v>12.011158124017321</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="0"/>
+        <v>38.408710592755156</v>
+      </c>
+      <c r="E67">
+        <v>10080596</v>
+      </c>
+      <c r="F67">
+        <v>20.397181381322241</v>
+      </c>
+      <c r="G67">
+        <f t="shared" si="1"/>
+        <v>24.36529227688078</v>
+      </c>
+      <c r="I67">
+        <v>10080492</v>
+      </c>
+      <c r="J67">
+        <v>46.107264141781577</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="2"/>
+        <v>7.6005492812430759</v>
+      </c>
+      <c r="M67">
+        <v>10080596</v>
+      </c>
+      <c r="N67">
+        <v>52.49933098184372</v>
+      </c>
+      <c r="O67">
+        <f t="shared" si="3"/>
+        <v>1.8854582379270752</v>
+      </c>
+      <c r="Q67">
+        <v>10080492</v>
+      </c>
+      <c r="R67">
+        <v>90.15734417292947</v>
+      </c>
+      <c r="S67">
+        <f t="shared" si="4"/>
+        <v>46.016718145091588</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B68" s="10">
+        <f>AVERAGE(B31:B67)</f>
+        <v>50.419868716772477</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F68" s="10">
+        <f>AVERAGE(F31:F67)</f>
+        <v>44.762473658203021</v>
+      </c>
+      <c r="I68">
+        <v>10080596</v>
+      </c>
+      <c r="J68">
+        <v>30.825674262907039</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="2"/>
+        <v>7.681040597631462</v>
+      </c>
+      <c r="M68">
+        <v>10080624</v>
+      </c>
+      <c r="N68">
+        <v>18.381076778735071</v>
+      </c>
+      <c r="O68">
+        <f t="shared" si="3"/>
+        <v>36.003712441035724</v>
+      </c>
+      <c r="Q68">
+        <v>10080596</v>
+      </c>
+      <c r="R68">
+        <v>42.707402943243352</v>
+      </c>
+      <c r="S68">
+        <f t="shared" si="4"/>
+        <v>1.4332230845945304</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" s="10">
+        <f>STDEVA(B31:B67)</f>
+        <v>17.822816814582147</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F69" s="10">
+        <f>STDEVA(F31:F67)</f>
+        <v>17.519153591461041</v>
+      </c>
+      <c r="I69">
+        <v>10080624</v>
+      </c>
+      <c r="J69">
+        <v>13.99913941381805</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="2"/>
+        <v>24.507575446720452</v>
+      </c>
+      <c r="M69">
+        <v>10080747</v>
+      </c>
+      <c r="N69">
+        <v>22.637414960253398</v>
+      </c>
+      <c r="O69">
+        <f t="shared" si="3"/>
+        <v>31.747374259517397</v>
+      </c>
+      <c r="Q69">
+        <v>10080747</v>
+      </c>
+      <c r="R69">
+        <v>30.887688883088689</v>
+      </c>
+      <c r="S69">
+        <f t="shared" si="4"/>
+        <v>13.252937144749193</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A70" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B70" s="10">
+        <f>SUM(C31:C67)/GETPIVOTDATA("Kurir",$A$2,"205_dt","2025-07-28 00:00:00.0")</f>
+        <v>11.695119497762946</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F70" s="10">
+        <f>SUM(G31:G67)/GETPIVOTDATA("Kurir",$A$2,"205_dt","2025-07-29 00:00:00.0")</f>
+        <v>12.399457070380604</v>
+      </c>
+      <c r="I70">
+        <v>10080747</v>
+      </c>
+      <c r="J70">
+        <v>13.61120888833336</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="2"/>
+        <v>24.895505972205143</v>
+      </c>
+      <c r="M70" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="N70" s="10">
+        <f>AVERAGE(N31:N69)</f>
+        <v>54.384789219770795</v>
+      </c>
+      <c r="Q70" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="R70" s="10">
+        <f>AVERAGE(R31:R69)</f>
+        <v>44.140626027837882</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I71" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="J71" s="10">
+        <f>AVERAGE(J31:J70)</f>
+        <v>38.506714860538501</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N71" s="10">
+        <f>STDEVA(N31:N69)</f>
+        <v>23.752670822733318</v>
+      </c>
+      <c r="Q71" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R71" s="10">
+        <f>STDEVA(R31:R69)</f>
+        <v>14.895351172721691</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I72" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J72" s="10">
+        <f>STDEVA(J31:J70)</f>
+        <v>19.873733763322655</v>
+      </c>
+      <c r="M72" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="N72" s="10">
+        <f>SUM(O31:O69)/GETPIVOTDATA("Kurir",$A$2,"205_dt","2025-08-07 00:00:00.0")</f>
+        <v>14.589962852248831</v>
+      </c>
+      <c r="Q72" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="R72" s="10">
+        <f>SUM(S31:S69)/GETPIVOTDATA("Kurir",$A$2,"205_dt","2025-08-20 00:00:00.0")</f>
+        <v>10.341184432904498</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I73" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J73" s="10">
+        <f>SUM(K31:K70)/GETPIVOTDATA("Kurir",$A$2,"205_dt","2025-08-06 00:00:00.0")</f>
+        <v>11.454700202146171</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
 </file>
--- a/3_Code/output/jarak_kurir_harian_dan_total_paket.xlsx
+++ b/3_Code/output/jarak_kurir_harian_dan_total_paket.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPB\TESIS\PENELITIAN\CODE\output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\tesis\3_Code\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E4CEE3-3046-4951-AA4F-A915F822AEEB}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B817A3FC-CC87-4932-A2EA-DC0EDF4D8F9F}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,13 +24,13 @@
   </definedNames>
   <calcPr calcId="179021"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="43">
   <si>
     <t>205_id</t>
   </si>
@@ -157,11 +157,17 @@
   <si>
     <t>AVG Paket</t>
   </si>
+  <si>
+    <t>Jain Fairness Index</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -237,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -259,53 +265,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -4384,7 +4349,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{21FB3EBC-14C7-4FAB-BF5B-B660E0644095}" name="PivotTable5" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{21FB3EBC-14C7-4FAB-BF5B-B660E0644095}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B43" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
@@ -4611,7 +4576,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87B6BFC0-8CFB-499E-ABAC-3ADB01F8CD8D}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87B6BFC0-8CFB-499E-ABAC-3ADB01F8CD8D}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A2:D26" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField dataField="1" showAll="0">
@@ -4788,7 +4753,7 @@
     <dataField name="Average of total_distance_km" fld="3" subtotal="average" baseField="1" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="0">
+    <format dxfId="11">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="2">
@@ -4798,7 +4763,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="2">
@@ -4808,7 +4773,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="9">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="2">
@@ -4818,7 +4783,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="2">
@@ -4828,7 +4793,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="7">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="1">
@@ -4837,7 +4802,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="1">
@@ -4860,7 +4825,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{17E076F9-C55C-451E-8131-7DFF3FC26389}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{17E076F9-C55C-451E-8131-7DFF3FC26389}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:D45" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -5085,7 +5050,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BECCD010-E5DB-46BD-A004-8CD073C51B46}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BECCD010-E5DB-46BD-A004-8CD073C51B46}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A2:D26" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField dataField="1" showAll="0">
@@ -5262,7 +5227,7 @@
     <dataField name="Average of total_distance_km" fld="3" subtotal="average" baseField="0" baseItem="1953018073"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="17">
+    <format dxfId="5">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="2">
@@ -5272,7 +5237,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="2">
@@ -5282,7 +5247,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="3">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="2">
@@ -5292,7 +5257,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="2">
@@ -5302,7 +5267,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="1">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="1">
@@ -5311,7 +5276,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="1">
@@ -6004,7 +5969,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A3C87F9-F0B4-48DF-B526-64D8EFC8A869}">
-  <dimension ref="A2:S73"/>
+  <dimension ref="A2:S74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -6501,7 +6466,7 @@
         <v>119</v>
       </c>
       <c r="C32">
-        <f t="shared" ref="C32:C70" si="0">ABS(B32-$B$68)</f>
+        <f t="shared" ref="C32:C67" si="0">ABS(B32-$B$68)</f>
         <v>17.027027027027032</v>
       </c>
       <c r="E32" s="3">
@@ -6511,7 +6476,7 @@
         <v>86</v>
       </c>
       <c r="G32">
-        <f t="shared" ref="G32:G70" si="1">ABS(F32-$F$68)</f>
+        <f t="shared" ref="G32:G67" si="1">ABS(F32-$F$68)</f>
         <v>4.7837837837837895</v>
       </c>
       <c r="I32" s="3">
@@ -6521,7 +6486,7 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <f t="shared" ref="K32:K73" si="2">ABS(J32-$J$71)</f>
+        <f t="shared" ref="K32:K70" si="2">ABS(J32-$J$71)</f>
         <v>21.5</v>
       </c>
       <c r="M32" s="3">
@@ -6531,7 +6496,7 @@
         <v>122</v>
       </c>
       <c r="O32">
-        <f t="shared" ref="O32:O72" si="3">ABS(N32-$N$70)</f>
+        <f t="shared" ref="O32:O69" si="3">ABS(N32-$N$70)</f>
         <v>22.282051282051285</v>
       </c>
       <c r="Q32" s="3">
@@ -6541,7 +6506,7 @@
         <v>101</v>
       </c>
       <c r="S32">
-        <f t="shared" ref="S32:S72" si="4">ABS(R32-$R$70)</f>
+        <f t="shared" ref="S32:S69" si="4">ABS(R32-$R$70)</f>
         <v>16.743589743589737</v>
       </c>
     </row>
@@ -8498,6 +8463,20 @@
       </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A71" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B71" s="13">
+        <f>(SUM($B$31:$B$67)^2)/(COUNT($B$31:$B$67)*(SUMSQ($B$31:$B$67)))</f>
+        <v>0.93467731456668202</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F71" s="13">
+        <f>(SUM($F$31:$F$67)^2)/(COUNT($F$31:$F$67)*(SUMSQ($F$31:$F$67)))</f>
+        <v>0.94144204960645639</v>
+      </c>
       <c r="I71" s="10" t="s">
         <v>41</v>
       </c>
@@ -8550,6 +8529,29 @@
       <c r="J73" s="10">
         <f>SUM(K31:K70)/COUNT(I31:I70)</f>
         <v>14.925000000000001</v>
+      </c>
+      <c r="M73" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="N73" s="13">
+        <f>(SUM($N$31:$N$69)^2)/(COUNT($N$31:$N$69)*(SUMSQ($N$31:$N$69)))</f>
+        <v>0.94277765300347538</v>
+      </c>
+      <c r="Q73" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="R73" s="13">
+        <f>(SUM($R$31:$R$69)^2)/(COUNT($R$31:$R$69)*(SUMSQ($R$31:$R$69)))</f>
+        <v>0.96103523909919086</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="I74" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J74" s="13">
+        <f>(SUM($J$31:$J$70)^2)/(COUNT($J$31:$J$70)*(SUMSQ($J$31:$J$70)))</f>
+        <v>0.94642226351922099</v>
       </c>
     </row>
   </sheetData>
